--- a/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_recalcmultiday.xlsx
+++ b/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_recalcmultiday.xlsx
@@ -41,6 +41,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
       </patternFill>
@@ -49,12 +55,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00CC3300"/>
         <bgColor rgb="00CC3300"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
     <fill>
@@ -137,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -152,16 +152,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -174,15 +174,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -796,16 +787,16 @@
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr"/>
-      <c r="D4" s="11" t="n">
+      <c r="D4" s="9" t="n">
         <v>31.7</v>
       </c>
-      <c r="E4" s="11" t="n">
+      <c r="E4" s="9" t="n">
         <v>16.9</v>
       </c>
-      <c r="F4" s="11" t="n">
+      <c r="F4" s="9" t="n">
         <v>24.3</v>
       </c>
-      <c r="G4" s="11" t="n">
+      <c r="G4" s="9" t="n">
         <v>14.8</v>
       </c>
       <c r="H4" s="3" t="n">
@@ -820,45 +811,51 @@
       <c r="K4" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="L4" s="3" t="n">
+      <c r="L4" s="9" t="n">
         <v>18.4</v>
       </c>
-      <c r="M4" s="11" t="n">
+      <c r="M4" s="9" t="n">
         <v>18.4</v>
       </c>
-      <c r="N4" s="3" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="P4" s="3" t="n">
+      <c r="N4" s="9" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="O4" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="P4" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" s="11" t="n">
+      <c r="Q4" s="9" t="n">
         <v>30.6</v>
       </c>
-      <c r="R4" s="3" t="n">
+      <c r="R4" s="9" t="n">
         <v>23.8</v>
       </c>
-      <c r="S4" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T4" s="3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="U4" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="V4" s="3" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="W4" s="11" t="n">
+      <c r="S4" s="9" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="T4" s="9" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="U4" s="9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="V4" s="9" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="W4" s="9" t="n">
         <v>24.9</v>
       </c>
-      <c r="X4" s="3" t="inlineStr"/>
-      <c r="Y4" s="3" t="inlineStr"/>
-      <c r="Z4" s="3" t="inlineStr"/>
+      <c r="X4" s="9" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="Y4" s="9" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="Z4" s="9" t="n">
+        <v>5.2</v>
+      </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>1</t>
@@ -873,17 +870,17 @@
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="11" t="n">
+      <c r="D5" s="9" t="n">
         <v>26.2</v>
       </c>
-      <c r="E5" s="11" t="n">
+      <c r="E5" s="9" t="n">
         <v>17.4</v>
       </c>
-      <c r="F5" s="11" t="n">
+      <c r="F5" s="9" t="n">
         <v>21.8</v>
       </c>
-      <c r="G5" s="3" t="n">
-        <v>81.8</v>
+      <c r="G5" s="9" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>17.3</v>
@@ -897,50 +894,50 @@
       <c r="K5" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L5" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="M5" s="11" t="n">
+      <c r="L5" s="9" t="n">
         <v>17.6</v>
       </c>
-      <c r="N5" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="P5" s="3" t="n">
+      <c r="M5" s="9" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="N5" s="9" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="O5" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="P5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" s="11" t="n">
+      <c r="Q5" s="9" t="n">
         <v>23.9</v>
       </c>
-      <c r="R5" s="3" t="n">
+      <c r="R5" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="S5" s="3" t="n">
+      <c r="S5" s="9" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="T5" s="9" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="U5" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="V5" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="T5" s="3" t="n">
-        <v>70.2</v>
-      </c>
-      <c r="U5" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="V5" s="3" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="W5" s="11" t="n">
+      <c r="W5" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="X5" s="3" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="Y5" s="3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="Z5" s="3" t="n">
-        <v>6.8</v>
+      <c r="X5" s="9" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="Y5" s="9" t="n">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="Z5" s="9" t="n">
+        <v>2.9</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -956,16 +953,16 @@
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr"/>
-      <c r="D6" s="11" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="E6" s="11" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="F6" s="11" t="n">
+      <c r="D6" s="9" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="F6" s="9" t="n">
         <v>24.6</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="G6" s="9" t="n">
         <v>15.2</v>
       </c>
       <c r="H6" s="3" t="n">
@@ -978,52 +975,52 @@
         <v>4.4</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="L6" s="3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L6" s="9" t="n">
         <v>17.4</v>
       </c>
-      <c r="M6" s="11" t="n">
+      <c r="M6" s="9" t="n">
         <v>17.5</v>
       </c>
-      <c r="N6" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>921.2</v>
-      </c>
-      <c r="P6" s="3" t="n">
+      <c r="N6" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="Q6" s="11" t="n">
+      <c r="O6" s="9" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="P6" s="9" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="Q6" s="9" t="n">
         <v>29.5</v>
       </c>
-      <c r="R6" s="3" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="S6" s="3" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="T6" s="3" t="n">
-        <v>390.6</v>
-      </c>
-      <c r="U6" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="V6" s="3" t="n">
+      <c r="R6" s="9" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="S6" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="T6" s="9" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="U6" s="9" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="V6" s="9" t="n">
         <v>27.2</v>
       </c>
-      <c r="W6" s="11" t="n">
+      <c r="W6" s="9" t="n">
         <v>22.6</v>
       </c>
-      <c r="X6" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="Y6" s="3" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="Z6" s="3" t="n">
-        <v>4</v>
+      <c r="X6" s="9" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="Y6" s="9" t="n">
+        <v>76</v>
+      </c>
+      <c r="Z6" s="9" t="n">
+        <v>8.699999999999999</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1039,20 +1036,20 @@
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="11" t="n">
+      <c r="D7" s="9" t="n">
         <v>30.5</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="F7" s="11" t="n">
+      <c r="F7" s="9" t="n">
         <v>25.2</v>
       </c>
-      <c r="G7" s="11" t="n">
+      <c r="G7" s="9" t="n">
         <v>10.6</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>1.4</v>
@@ -1061,52 +1058,52 @@
         <v>2.3</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="L7" s="3" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="L7" s="9" t="n">
         <v>20.3</v>
       </c>
-      <c r="M7" s="11" t="n">
+      <c r="M7" s="9" t="n">
         <v>20.2</v>
       </c>
-      <c r="N7" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>90.2</v>
-      </c>
-      <c r="P7" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q7" s="11" t="n">
+      <c r="N7" s="9" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="O7" s="9" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="P7" s="9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q7" s="9" t="n">
         <v>20.1</v>
       </c>
-      <c r="R7" s="11" t="n">
+      <c r="R7" s="9" t="n">
         <v>19.5</v>
       </c>
-      <c r="S7" s="11" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="T7" s="11" t="n">
-        <v>96.2</v>
-      </c>
-      <c r="U7" s="11" t="n">
+      <c r="S7" s="9" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T7" s="9" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="U7" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="V7" s="3" t="n">
+      <c r="V7" s="9" t="n">
         <v>21.4</v>
       </c>
-      <c r="W7" s="11" t="n">
+      <c r="W7" s="9" t="n">
         <v>20.6</v>
       </c>
-      <c r="X7" s="3" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="Y7" s="3" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="Z7" s="3" t="n">
-        <v>23.8</v>
+      <c r="X7" s="9" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="Y7" s="9" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="Z7" s="9" t="n">
+        <v>1.2</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1122,16 +1119,16 @@
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="11" t="n">
+      <c r="D8" s="9" t="n">
         <v>26.8</v>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="9" t="n">
         <v>18.4</v>
       </c>
-      <c r="F8" s="11" t="n">
+      <c r="F8" s="9" t="n">
         <v>22.6</v>
       </c>
-      <c r="G8" s="11" t="n">
+      <c r="G8" s="9" t="n">
         <v>8.4</v>
       </c>
       <c r="H8" s="3" t="n">
@@ -1146,48 +1143,50 @@
       <c r="K8" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="L8" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="M8" s="11" t="n">
+      <c r="M8" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="N8" s="3" t="inlineStr"/>
-      <c r="O8" s="3" t="n">
-        <v>791.2</v>
-      </c>
-      <c r="P8" s="3" t="n">
+      <c r="N8" s="9" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="O8" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="P8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" s="11" t="n">
+      <c r="Q8" s="9" t="n">
         <v>25.8</v>
       </c>
-      <c r="R8" s="3" t="n">
+      <c r="R8" s="9" t="n">
         <v>22.3</v>
       </c>
-      <c r="S8" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="T8" s="3" t="n">
-        <v>66.2</v>
-      </c>
-      <c r="U8" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="V8" s="3" t="n">
+      <c r="S8" s="9" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="T8" s="9" t="n">
+        <v>81</v>
+      </c>
+      <c r="U8" s="9" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="V8" s="9" t="n">
         <v>24.6</v>
       </c>
-      <c r="W8" s="11" t="n">
+      <c r="W8" s="9" t="n">
         <v>21.4</v>
       </c>
-      <c r="X8" s="3" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="Y8" s="3" t="n">
-        <v>86.2</v>
-      </c>
-      <c r="Z8" s="3" t="n">
-        <v>27.3</v>
+      <c r="X8" s="9" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="Y8" s="9" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="Z8" s="9" t="n">
+        <v>5.5</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1203,16 +1202,16 @@
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="11" t="n">
-        <v>147.5</v>
-      </c>
-      <c r="E9" s="11" t="n">
-        <v>89.5</v>
-      </c>
-      <c r="F9" s="11" t="n">
+      <c r="D9" s="9" t="n">
+        <v>147.4</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="F9" s="9" t="n">
         <v>118.5</v>
       </c>
-      <c r="G9" s="3" t="n">
+      <c r="G9" s="9" t="n">
         <v>57.8</v>
       </c>
       <c r="H9" s="3" t="n">
@@ -1222,31 +1221,31 @@
         <v>9.6</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="K9" s="18" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="K9" s="15" t="n">
         <v>44.1</v>
       </c>
-      <c r="L9" s="18" t="n">
+      <c r="L9" s="9" t="n">
         <v>92.59999999999999</v>
       </c>
-      <c r="M9" s="11" t="n">
+      <c r="M9" s="9" t="n">
         <v>92.59999999999999</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>451.2</v>
+        <v>454.2</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q9" s="11" t="n">
+      <c r="Q9" s="9" t="n">
         <v>129.9</v>
       </c>
-      <c r="R9" s="18" t="n">
-        <v>110.1</v>
+      <c r="R9" s="9" t="n">
+        <v>110.7</v>
       </c>
       <c r="S9" s="3" t="n">
         <v>122.3</v>
@@ -1257,10 +1256,10 @@
       <c r="U9" s="3" t="n">
         <v>48.8</v>
       </c>
-      <c r="V9" s="18" t="n">
+      <c r="V9" s="9" t="n">
         <v>123.8</v>
       </c>
-      <c r="W9" s="11" t="n">
+      <c r="W9" s="9" t="n">
         <v>110.8</v>
       </c>
       <c r="X9" s="3" t="n">
@@ -1286,16 +1285,16 @@
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr"/>
-      <c r="D10" s="11" t="n">
+      <c r="D10" s="9" t="n">
         <v>29.5</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="F10" s="11" t="n">
+      <c r="F10" s="9" t="n">
         <v>23.7</v>
       </c>
-      <c r="G10" s="11" t="n">
+      <c r="G10" s="9" t="n">
         <v>11.6</v>
       </c>
       <c r="H10" s="3" t="n">
@@ -1305,55 +1304,55 @@
         <v>1.9</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L10" s="18" t="n">
+      <c r="L10" s="9" t="n">
         <v>18.5</v>
       </c>
-      <c r="M10" s="11" t="n">
+      <c r="M10" s="9" t="n">
         <v>18.5</v>
       </c>
-      <c r="N10" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="P10" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q10" s="11" t="n">
+      <c r="N10" s="9" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="O10" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="P10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="9" t="n">
         <v>25.9</v>
       </c>
-      <c r="R10" s="18" t="n">
+      <c r="R10" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="S10" s="3" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="T10" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="U10" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="V10" s="18" t="n">
+      <c r="S10" s="9" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="T10" s="9" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="U10" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="V10" s="9" t="n">
         <v>24.8</v>
       </c>
-      <c r="W10" s="11" t="n">
+      <c r="W10" s="9" t="n">
         <v>22.2</v>
       </c>
-      <c r="X10" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z10" s="3" t="n">
-        <v>62.8</v>
+      <c r="X10" s="9" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="Y10" s="9" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="Z10" s="9" t="n">
+        <v>4.5</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1369,29 +1368,29 @@
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="11" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="E11" s="11" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="F11" s="11" t="n">
+      <c r="D11" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F11" s="9" t="n">
         <v>23.8</v>
       </c>
-      <c r="G11" s="11" t="n">
+      <c r="G11" s="9" t="n">
         <v>10.5</v>
       </c>
       <c r="H11" s="3" t="inlineStr"/>
       <c r="I11" s="3" t="n">
-        <v>11.3</v>
+        <v>1.7</v>
       </c>
       <c r="J11" s="3" t="inlineStr"/>
       <c r="K11" s="3" t="inlineStr"/>
       <c r="L11" s="3" t="n">
         <v>8.4</v>
       </c>
-      <c r="M11" s="17" t="n">
-        <v>24.3</v>
+      <c r="M11" s="3" t="n">
+        <v>12.3</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>2.8</v>
@@ -1400,27 +1399,27 @@
         <v>91.59999999999999</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="9" t="n">
         <v>28.4</v>
       </c>
-      <c r="R11" s="3" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="S11" s="3" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="T11" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="U11" s="3" t="n">
-        <v>12</v>
+      <c r="R11" s="9" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="S11" s="9" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="T11" s="9" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="U11" s="9" t="n">
+        <v>9.199999999999999</v>
       </c>
       <c r="V11" s="3" t="n">
         <v>28.9</v>
       </c>
-      <c r="W11" s="11" t="n">
+      <c r="W11" s="9" t="n">
         <v>22.9</v>
       </c>
       <c r="X11" s="3" t="n">
@@ -1446,74 +1445,74 @@
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr"/>
-      <c r="D12" s="11" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="E12" s="11" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="F12" s="11" t="n">
+      <c r="D12" s="9" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="F12" s="9" t="n">
         <v>22.4</v>
       </c>
-      <c r="G12" s="15" t="n">
-        <v>98.40000000000001</v>
+      <c r="G12" s="9" t="n">
+        <v>8.1</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>17.5</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>2.8</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="L12" s="15" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>90.2</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Q12" s="15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R12" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q12" s="9" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="R12" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="S12" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T12" s="3" t="n">
-        <v>61.3</v>
-      </c>
-      <c r="U12" s="3" t="n">
-        <v>0.5</v>
+      <c r="S12" s="9" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="T12" s="9" t="n">
+        <v>87</v>
+      </c>
+      <c r="U12" s="9" t="n">
+        <v>3.9</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="W12" s="11" t="n">
-        <v>21.9</v>
+      <c r="W12" s="9" t="n">
+        <v>21.1</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>2.4</v>
+        <v>24.4</v>
       </c>
       <c r="Y12" s="3" t="n">
         <v>81.2</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>82.2</v>
+        <v>83.2</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1529,17 +1528,17 @@
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr"/>
-      <c r="D13" s="3" t="n">
+      <c r="D13" s="9" t="n">
         <v>26.8</v>
       </c>
-      <c r="E13" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="F13" s="3" t="n">
+      <c r="E13" s="9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F13" s="9" t="n">
         <v>22.7</v>
       </c>
-      <c r="G13" s="3" t="n">
-        <v>89.3</v>
+      <c r="G13" s="9" t="n">
+        <v>8.300000000000001</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>17.6</v>
@@ -1548,55 +1547,55 @@
         <v>2.5</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>2.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L13" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="M13" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>9</v>
+        <v>90.2</v>
       </c>
       <c r="P13" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q13" s="3" t="n">
+      <c r="Q13" s="9" t="n">
         <v>22.2</v>
       </c>
-      <c r="R13" s="3" t="n">
+      <c r="R13" s="9" t="n">
         <v>20.4</v>
       </c>
-      <c r="S13" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="T13" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="U13" s="3" t="n">
-        <v>31.8</v>
+      <c r="S13" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="T13" s="9" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="U13" s="9" t="n">
+        <v>2.8</v>
       </c>
       <c r="V13" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="W13" s="11" t="n">
+      <c r="W13" s="9" t="n">
         <v>20</v>
       </c>
       <c r="X13" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>12</v>
+        <v>2.2</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>12.5</v>
+        <v>2.5</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1612,19 +1611,19 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D14" s="11" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="D14" s="9" t="n">
         <v>29.9</v>
       </c>
-      <c r="E14" s="11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="F14" s="11" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>19.5</v>
+      <c r="E14" s="9" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="G14" s="9" t="n">
+        <v>11.5</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>15.5</v>
@@ -1636,7 +1635,7 @@
         <v>2.7</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>18.2</v>
+        <v>22.5</v>
       </c>
       <c r="L14" s="3" t="n">
         <v>18.9</v>
@@ -1645,7 +1644,7 @@
         <v>18.7</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>0.2</v>
+        <v>2.1</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>91.2</v>
@@ -1653,35 +1652,35 @@
       <c r="P14" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q14" s="3" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="R14" s="3" t="n">
+      <c r="Q14" s="9" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="R14" s="9" t="n">
         <v>23.4</v>
       </c>
-      <c r="S14" s="3" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="T14" s="3" t="n">
-        <v>58.2</v>
-      </c>
-      <c r="U14" s="3" t="n">
-        <v>11</v>
+      <c r="S14" s="9" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="T14" s="9" t="n">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="U14" s="9" t="n">
+        <v>8.4</v>
       </c>
       <c r="V14" s="3" t="n">
         <v>25.1</v>
       </c>
-      <c r="W14" s="11" t="n">
+      <c r="W14" s="9" t="n">
         <v>22.8</v>
       </c>
       <c r="X14" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>27.2</v>
+        <v>77.2</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>51.4</v>
+        <v>5.4</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1697,23 +1696,23 @@
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr"/>
-      <c r="D15" s="11" t="n">
+      <c r="D15" s="9" t="n">
         <v>28.3</v>
       </c>
-      <c r="E15" s="11" t="n">
+      <c r="E15" s="9" t="n">
         <v>18.6</v>
       </c>
-      <c r="F15" s="11" t="n">
+      <c r="F15" s="9" t="n">
         <v>23.5</v>
       </c>
-      <c r="G15" s="11" t="n">
+      <c r="G15" s="9" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="H15" s="17" t="n">
+      <c r="H15" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>9.6</v>
+        <v>8.5</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>2.7</v>
@@ -1728,7 +1727,7 @@
         <v>18.9</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>2.5</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>91.2</v>
@@ -1736,25 +1735,25 @@
       <c r="P15" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q15" s="15" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R15" s="3" t="n">
+      <c r="Q15" s="9" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="R15" s="9" t="n">
         <v>22.9</v>
       </c>
-      <c r="S15" s="3" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="T15" s="3" t="n">
-        <v>58.2</v>
-      </c>
-      <c r="U15" s="3" t="n">
-        <v>9.1</v>
+      <c r="S15" s="9" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="T15" s="9" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="U15" s="9" t="n">
+        <v>6.9</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="W15" s="11" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="W15" s="9" t="n">
         <v>20.9</v>
       </c>
       <c r="X15" s="3" t="n">
@@ -1764,7 +1763,7 @@
         <v>8.5</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1780,48 +1779,48 @@
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr"/>
-      <c r="D16" s="18" t="n">
-        <v>14</v>
-      </c>
-      <c r="E16" s="18" t="n">
-        <v>112.3</v>
-      </c>
-      <c r="F16" s="18" t="n">
+      <c r="D16" s="9" t="n">
+        <v>140.4</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="F16" s="9" t="n">
         <v>116.6</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>81.5</v>
+        <v>87.5</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>29.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>14.3</v>
       </c>
       <c r="K16" s="12" t="inlineStr"/>
-      <c r="L16" s="18" t="n">
+      <c r="L16" s="15" t="n">
         <v>95.3</v>
       </c>
-      <c r="M16" s="18" t="n">
+      <c r="M16" s="15" t="n">
         <v>94.59999999999999</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>1</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>853.2</v>
+        <v>53.2</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q16" s="18" t="n">
-        <v>127.2</v>
-      </c>
-      <c r="R16" s="18" t="n">
-        <v>122.3</v>
+      <c r="Q16" s="9" t="n">
+        <v>129.2</v>
+      </c>
+      <c r="R16" s="9" t="n">
+        <v>112.5</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>126.6</v>
@@ -1830,19 +1829,19 @@
         <v>38.2</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>99.2</v>
-      </c>
-      <c r="V16" s="18" t="n">
-        <v>187.8</v>
-      </c>
-      <c r="W16" s="11" t="n">
-        <v>108.5</v>
+        <v>49.2</v>
+      </c>
+      <c r="V16" s="15" t="n">
+        <v>114</v>
+      </c>
+      <c r="W16" s="9" t="n">
+        <v>107.7</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>124.6</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>970.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>15</v>
@@ -1860,18 +1859,20 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr"/>
-      <c r="D17" s="18" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="E17" s="18" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="F17" s="15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>9.1</v>
+      <c r="C17" s="3" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F17" s="9" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="G17" s="9" t="n">
+        <v>9.6</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>12.5</v>
@@ -1880,43 +1881,43 @@
         <v>1.9</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>22.9</v>
+        <v>2.8</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="18" t="n">
+      <c r="L17" s="15" t="n">
         <v>19.9</v>
       </c>
-      <c r="M17" s="18" t="n">
-        <v>18.5</v>
+      <c r="M17" s="15" t="n">
+        <v>18.8</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>21.2</v>
+        <v>91.2</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q17" s="18" t="n">
+      <c r="Q17" s="9" t="n">
         <v>25.8</v>
       </c>
-      <c r="R17" s="18" t="n">
+      <c r="R17" s="9" t="n">
         <v>22.5</v>
       </c>
-      <c r="S17" s="3" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="T17" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="U17" s="3" t="n">
-        <v>82.2</v>
-      </c>
-      <c r="V17" s="18" t="n">
+      <c r="S17" s="9" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="T17" s="9" t="n">
+        <v>82</v>
+      </c>
+      <c r="U17" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="V17" s="15" t="n">
         <v>22.9</v>
       </c>
-      <c r="W17" s="11" t="n">
+      <c r="W17" s="9" t="n">
         <v>21.5</v>
       </c>
       <c r="X17" s="3" t="n">
@@ -1942,20 +1943,20 @@
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr"/>
-      <c r="D18" s="11" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="E18" s="11" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="F18" s="11" t="n">
-        <v>19.4</v>
+      <c r="D18" s="9" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E18" s="9" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="F18" s="9" t="n">
+        <v>22.3</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>12.4</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>12.6</v>
+        <v>15.5</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>2.1</v>
@@ -1966,22 +1967,22 @@
       <c r="K18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="3" t="n">
+      <c r="L18" s="9" t="n">
         <v>19.2</v>
       </c>
-      <c r="M18" s="15" t="n">
-        <v>1.3</v>
+      <c r="M18" s="14" t="n">
+        <v>1.1</v>
       </c>
       <c r="N18" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>291.2</v>
+        <v>91.2</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q18" s="15" t="n">
+      <c r="Q18" s="14" t="n">
         <v>89.2</v>
       </c>
       <c r="R18" s="3" t="n">
@@ -1996,7 +1997,7 @@
       <c r="U18" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="V18" s="3" t="n">
+      <c r="V18" s="9" t="n">
         <v>21.8</v>
       </c>
       <c r="W18" s="3" t="n">
@@ -2027,20 +2028,20 @@
       <c r="C19" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="D19" s="11" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="E19" s="11" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="F19" s="11" t="n">
-        <v>24</v>
-      </c>
-      <c r="G19" s="11" t="n">
+      <c r="D19" s="9" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="F19" s="9" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="G19" s="9" t="n">
         <v>12.9</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>15.4</v>
+        <v>16.4</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>1.5</v>
@@ -2051,19 +2052,19 @@
       <c r="K19" s="3" t="n">
         <v>27.9</v>
       </c>
-      <c r="L19" s="3" t="n">
+      <c r="L19" s="9" t="n">
         <v>18.3</v>
       </c>
-      <c r="M19" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="N19" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="O19" s="3" t="n">
-        <v>92.2</v>
-      </c>
-      <c r="P19" s="3" t="n">
+      <c r="M19" s="9" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="N19" s="9" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="O19" s="9" t="n">
+        <v>99</v>
+      </c>
+      <c r="P19" s="9" t="n">
         <v>0.2</v>
       </c>
       <c r="Q19" s="3" t="n">
@@ -2076,24 +2077,24 @@
         <v>23</v>
       </c>
       <c r="T19" s="3" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="U19" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="V19" s="9" t="n">
         <v>20.2</v>
       </c>
-      <c r="U19" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="V19" s="3" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="W19" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="X19" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="Y19" s="3" t="n">
-        <v>81.8</v>
-      </c>
-      <c r="Z19" s="3" t="n">
+      <c r="W19" s="9" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="X19" s="9" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="Y19" s="9" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="Z19" s="9" t="n">
         <v>0.6</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
@@ -2110,19 +2111,19 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="D20" s="11" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="E20" s="11" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="F20" s="11" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="G20" s="17" t="n">
-        <v>59.6</v>
+        <v>10.1</v>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="F20" s="9" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>0.9</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>17.6</v>
@@ -2136,42 +2137,44 @@
       <c r="K20" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L20" s="17" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="M20" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="N20" s="3" t="inlineStr"/>
-      <c r="O20" s="3" t="n">
-        <v>99.2</v>
-      </c>
-      <c r="P20" s="3" t="n">
+      <c r="L20" s="9" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="M20" s="9" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="N20" s="9" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="O20" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="P20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" s="15" t="n">
+      <c r="Q20" s="14" t="n">
         <v>2.6</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>21.9</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>20.7</v>
+        <v>23.7</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>22.2</v>
+        <v>72.2</v>
       </c>
       <c r="U20" s="3" t="n">
         <v>10.3</v>
       </c>
-      <c r="V20" s="3" t="n">
+      <c r="V20" s="9" t="n">
         <v>22.8</v>
       </c>
       <c r="W20" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="X20" s="17" t="n">
-        <v>23.2</v>
+      <c r="X20" s="3" t="n">
+        <v>85.2</v>
       </c>
       <c r="Y20" s="3" t="n">
         <v>2.6</v>
@@ -2195,16 +2198,16 @@
       <c r="C21" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="D21" s="11" t="n">
+      <c r="D21" s="9" t="n">
         <v>28.4</v>
       </c>
-      <c r="E21" s="11" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="F21" s="11" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="G21" s="3" t="n">
+      <c r="E21" s="9" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="G21" s="9" t="n">
         <v>10.3</v>
       </c>
       <c r="H21" s="3" t="n">
@@ -2219,13 +2222,15 @@
       <c r="K21" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="L21" s="3" t="n">
+      <c r="L21" s="9" t="n">
         <v>19.4</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="N21" s="3" t="inlineStr"/>
+      <c r="N21" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="O21" s="3" t="n">
         <v>92.2</v>
       </c>
@@ -2235,31 +2240,31 @@
       <c r="Q21" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="R21" s="15" t="n">
-        <v>1.3</v>
+      <c r="R21" s="3" t="n">
+        <v>12.1</v>
       </c>
       <c r="S21" s="3" t="n">
         <v>22</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>88.7</v>
+        <v>88.2</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="V21" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="W21" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="V21" s="9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="W21" s="9" t="n">
         <v>19.1</v>
       </c>
-      <c r="X21" s="3" t="n">
+      <c r="X21" s="9" t="n">
         <v>21.9</v>
       </c>
-      <c r="Y21" s="3" t="n">
-        <v>90.3</v>
-      </c>
-      <c r="Z21" s="3" t="n">
+      <c r="Y21" s="9" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="Z21" s="9" t="n">
         <v>0.8</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
@@ -2278,23 +2283,23 @@
       <c r="C22" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="D22" s="11" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="E22" s="11" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="F22" s="11" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="G22" s="3" t="n">
+      <c r="D22" s="9" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="F22" s="9" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="G22" s="9" t="n">
         <v>12.2</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>1.5</v>
+        <v>15.9</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="J22" s="3" t="n">
         <v>3.2</v>
@@ -2302,38 +2307,38 @@
       <c r="K22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="M22" s="3" t="n">
+      <c r="L22" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="N22" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="O22" s="3" t="n">
-        <v>991.2</v>
-      </c>
-      <c r="P22" s="3" t="n">
+      <c r="M22" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="N22" s="9" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="O22" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="P22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" s="15" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R22" s="15" t="n">
-        <v>2.2</v>
+      <c r="Q22" s="3" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>23.1</v>
       </c>
       <c r="S22" s="3" t="n">
         <v>25</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>86.2</v>
+        <v>56.2</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>13.9</v>
       </c>
-      <c r="V22" s="15" t="n">
-        <v>2.4</v>
+      <c r="V22" s="9" t="n">
+        <v>24.6</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>26.2</v>
@@ -2361,47 +2366,47 @@
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr"/>
-      <c r="D23" s="11" t="n">
-        <v>142.5</v>
-      </c>
-      <c r="E23" s="11" t="n">
-        <v>85.5</v>
-      </c>
-      <c r="F23" s="11" t="n">
-        <v>114</v>
-      </c>
-      <c r="G23" s="3" t="n">
+      <c r="D23" s="9" t="n">
+        <v>142.6</v>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="F23" s="9" t="n">
+        <v>116.5</v>
+      </c>
+      <c r="G23" s="9" t="n">
         <v>52.2</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>23.8</v>
+        <v>83.8</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>12.6</v>
+        <v>7.6</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="K23" s="18" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="L23" s="18" t="n">
-        <v>93.90000000000001</v>
-      </c>
-      <c r="M23" s="18" t="n">
-        <v>1952.9</v>
+      <c r="K23" s="15" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="L23" s="9" t="n">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="M23" s="15" t="n">
+        <v>92.90000000000001</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>951.2</v>
+        <v>458.2</v>
       </c>
       <c r="P23" s="3" t="inlineStr"/>
-      <c r="Q23" s="18" t="n">
+      <c r="Q23" s="15" t="n">
         <v>121</v>
       </c>
-      <c r="R23" s="18" t="n">
+      <c r="R23" s="15" t="n">
         <v>107.2</v>
       </c>
       <c r="S23" s="3" t="n">
@@ -2413,17 +2418,17 @@
       <c r="U23" s="3" t="n">
         <v>37.7</v>
       </c>
-      <c r="V23" s="18" t="n">
-        <v>108.4</v>
-      </c>
-      <c r="W23" s="18" t="n">
+      <c r="V23" s="9" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="W23" s="15" t="n">
         <v>102.6</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>198.7</v>
+        <v>117.7</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>9425.6</v>
+        <v>27.6</v>
       </c>
       <c r="Z23" s="3" t="n">
         <v>12.7</v>
@@ -2442,66 +2447,66 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D24" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D24" s="9" t="n">
         <v>28.5</v>
       </c>
-      <c r="E24" s="11" t="n">
+      <c r="E24" s="9" t="n">
         <v>17.1</v>
       </c>
-      <c r="F24" s="11" t="n">
+      <c r="F24" s="9" t="n">
         <v>22.8</v>
       </c>
-      <c r="G24" s="11" t="n">
+      <c r="G24" s="9" t="n">
         <v>11.4</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>1.5</v>
+        <v>0.2</v>
       </c>
       <c r="J24" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="K24" s="17" t="n">
-        <v>65.59999999999999</v>
-      </c>
-      <c r="L24" s="18" t="n">
-        <v>98.8</v>
-      </c>
-      <c r="M24" s="18" t="n">
+      <c r="K24" s="8" t="n">
+        <v>991999.1</v>
+      </c>
+      <c r="L24" s="9" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="M24" s="9" t="n">
         <v>18.6</v>
       </c>
-      <c r="N24" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O24" s="3" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="P24" s="3" t="n">
+      <c r="N24" s="9" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="O24" s="9" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="P24" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q24" s="18" t="n">
+      <c r="Q24" s="15" t="n">
         <v>27.2</v>
       </c>
-      <c r="R24" s="18" t="n">
-        <v>21.6</v>
+      <c r="R24" s="15" t="n">
+        <v>2.4</v>
       </c>
       <c r="S24" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>72.3</v>
+        <v>72.2</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>6.9</v>
       </c>
-      <c r="V24" s="18" t="n">
+      <c r="V24" s="9" t="n">
         <v>21.7</v>
       </c>
-      <c r="W24" s="18" t="n">
+      <c r="W24" s="15" t="n">
         <v>20.5</v>
       </c>
       <c r="X24" s="3" t="n">
@@ -2511,7 +2516,7 @@
         <v>2.5</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>85.8</v>
+        <v>8.5</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2527,20 +2532,20 @@
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr"/>
-      <c r="D25" s="11" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="E25" s="11" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="F25" s="11" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="G25" s="15" t="n">
+      <c r="D25" s="9" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="F25" s="9" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="G25" s="14" t="n">
         <v>44.4</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>17.9</v>
+        <v>17.1</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>2.1</v>
@@ -2551,47 +2556,47 @@
       <c r="K25" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L25" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="M25" s="17" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="N25" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="O25" s="3" t="n">
-        <v>59.2</v>
-      </c>
-      <c r="P25" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q25" s="15" t="n">
+      <c r="L25" s="9" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="M25" s="9" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="N25" s="9" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="O25" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="P25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="14" t="n">
         <v>2.6</v>
       </c>
-      <c r="R25" s="15" t="n">
+      <c r="R25" s="14" t="n">
         <v>3</v>
       </c>
       <c r="S25" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>31.2</v>
+        <v>71.2</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="V25" s="11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="V25" s="3" t="n">
         <v>25.3</v>
       </c>
-      <c r="W25" s="15" t="n">
+      <c r="W25" s="14" t="n">
         <v>4.9</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>23.9</v>
+        <v>23.2</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>69.3</v>
+        <v>67.2</v>
       </c>
       <c r="Z25" s="3" t="inlineStr"/>
       <c r="AA25" s="3" t="inlineStr">
@@ -2608,22 +2613,22 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>111.6</v>
-      </c>
-      <c r="D26" s="11" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="E26" s="11" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="F26" s="11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="E26" s="9" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="F26" s="9" t="n">
         <v>23.9</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>9.4</v>
+        <v>28.4</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>1.6</v>
+        <v>16.7</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>1.2</v>
@@ -2634,17 +2639,17 @@
       <c r="K26" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="L26" s="3" t="n">
+      <c r="L26" s="9" t="n">
         <v>19.6</v>
       </c>
-      <c r="M26" s="15" t="n">
-        <v>98.96000000000001</v>
+      <c r="M26" s="3" t="n">
+        <v>29.9</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>8.1</v>
+        <v>9.1</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>0</v>
@@ -2656,7 +2661,7 @@
         <v>23.3</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>17.9</v>
+        <v>27.1</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>76.2</v>
@@ -2664,7 +2669,7 @@
       <c r="U26" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="V26" s="11" t="n">
+      <c r="V26" s="3" t="n">
         <v>20.9</v>
       </c>
       <c r="W26" s="3" t="n">
@@ -2693,47 +2698,47 @@
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr"/>
-      <c r="D27" s="11" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="E27" s="11" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="F27" s="11" t="n">
+      <c r="D27" s="9" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="E27" s="9" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="F27" s="9" t="n">
         <v>22.4</v>
       </c>
-      <c r="G27" s="11" t="n">
-        <v>9.800000000000001</v>
+      <c r="G27" s="9" t="n">
+        <v>9.9</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>19.8</v>
+        <v>1.9</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="L27" s="3" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="L27" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="M27" s="15" t="n">
+      <c r="M27" s="14" t="n">
         <v>1.8</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>1.8</v>
+        <v>19.1</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>922.2</v>
+        <v>98.2</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>26.6</v>
+        <v>20.6</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>22.1</v>
@@ -2742,12 +2747,12 @@
         <v>23.9</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>63.2</v>
+        <v>2.5</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="V27" s="11" t="n">
+      <c r="V27" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="W27" s="3" t="n">
@@ -2776,17 +2781,17 @@
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr"/>
-      <c r="D28" s="11" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="E28" s="11" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="F28" s="11" t="n">
+      <c r="D28" s="9" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="E28" s="9" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="F28" s="9" t="n">
         <v>24.3</v>
       </c>
-      <c r="G28" s="3" t="n">
-        <v>15.8</v>
+      <c r="G28" s="9" t="n">
+        <v>16.8</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>14</v>
@@ -2800,23 +2805,23 @@
       <c r="K28" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="L28" s="15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M28" s="15" t="n">
-        <v>1.6</v>
+      <c r="L28" s="9" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="M28" s="3" t="n">
+        <v>16.8</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>14.8</v>
+        <v>1.8</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>92.2</v>
+        <v>92.8</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>20.9</v>
+        <v>20.1</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>23.3</v>
@@ -2825,19 +2830,19 @@
         <v>24.5</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>4</v>
+        <v>40.2</v>
       </c>
       <c r="U28" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="V28" s="11" t="n">
+      <c r="V28" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="W28" s="15" t="n">
-        <v>2.1</v>
+      <c r="W28" s="3" t="n">
+        <v>21.1</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>21.2</v>
+        <v>20.2</v>
       </c>
       <c r="Y28" s="3" t="n">
         <v>14.6</v>
@@ -2859,14 +2864,14 @@
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr"/>
-      <c r="D29" s="11" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="E29" s="11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="F29" s="11" t="n">
-        <v>24.2</v>
+      <c r="D29" s="9" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F29" s="9" t="n">
+        <v>24.3</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>19.7</v>
@@ -2883,15 +2888,15 @@
       <c r="K29" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="L29" s="3" t="n">
-        <v>19.2</v>
+      <c r="L29" s="9" t="n">
+        <v>18.2</v>
       </c>
       <c r="M29" s="13" t="inlineStr"/>
       <c r="N29" s="3" t="n">
-        <v>0.1</v>
+        <v>9.6</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>90.2</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>0</v>
@@ -2903,16 +2908,16 @@
         <v>21.2</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>14.5</v>
+        <v>24.5</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>12.2</v>
+        <v>72.2</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="V29" s="11" t="n">
-        <v>13.4</v>
+      <c r="V29" s="3" t="n">
+        <v>19.4</v>
       </c>
       <c r="W29" s="3" t="n">
         <v>21.8</v>
@@ -2924,7 +2929,7 @@
         <v>2.3</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>20.1</v>
+        <v>20.5</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2940,69 +2945,69 @@
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr"/>
-      <c r="D30" s="11" t="n">
-        <v>150.8</v>
-      </c>
-      <c r="E30" s="11" t="n">
-        <v>87.90000000000001</v>
-      </c>
-      <c r="F30" s="11" t="n">
+      <c r="D30" s="9" t="n">
+        <v>148.4</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="F30" s="9" t="n">
         <v>119</v>
       </c>
-      <c r="G30" s="3" t="n">
-        <v>5.8</v>
+      <c r="G30" s="9" t="n">
+        <v>58.8</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>80.59999999999999</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>10.9</v>
+        <v>10.5</v>
       </c>
       <c r="J30" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="K30" s="18" t="n">
+      <c r="K30" s="15" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="L30" s="18" t="n">
-        <v>292.5</v>
-      </c>
-      <c r="M30" s="18" t="n">
-        <v>392.1</v>
+      <c r="L30" s="9" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="M30" s="15" t="n">
+        <v>9.199999999999999</v>
       </c>
       <c r="N30" s="3" t="inlineStr"/>
       <c r="O30" s="3" t="n">
-        <v>45.1</v>
+        <v>45.7</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" s="18" t="n">
+      <c r="Q30" s="15" t="n">
         <v>130.7</v>
       </c>
-      <c r="R30" s="18" t="n">
-        <v>112.9</v>
+      <c r="R30" s="15" t="n">
+        <v>12.9</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>126.4</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>322.2</v>
+        <v>222.2</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>118.2</v>
-      </c>
-      <c r="V30" s="11" t="n">
-        <v>104.5</v>
-      </c>
-      <c r="W30" s="18" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="V30" s="15" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="W30" s="15" t="n">
         <v>114.6</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>312.2</v>
+        <v>372.2</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>52.4</v>
+        <v>32.4</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>33</v>
@@ -3021,47 +3026,47 @@
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr"/>
-      <c r="D31" s="11" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="E31" s="11" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="F31" s="11" t="n">
-        <v>23.8</v>
+      <c r="D31" s="9" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="F31" s="9" t="n">
+        <v>23.9</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>18.1</v>
+        <v>16.1</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>2.1</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="18" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="M31" s="18" t="n">
+      <c r="L31" s="9" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="M31" s="9" t="n">
         <v>18.5</v>
       </c>
-      <c r="N31" s="3" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="O31" s="3" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="P31" s="3" t="n">
+      <c r="N31" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="O31" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="P31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" s="18" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="R31" s="18" t="n">
+      <c r="Q31" s="15" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="R31" s="15" t="n">
         <v>22.6</v>
       </c>
       <c r="S31" s="3" t="n">
@@ -3073,14 +3078,14 @@
       <c r="U31" s="3" t="n">
         <v>8.9</v>
       </c>
-      <c r="V31" s="11" t="n">
+      <c r="V31" s="15" t="n">
         <v>20.8</v>
       </c>
-      <c r="W31" s="18" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="X31" s="17" t="n">
-        <v>47.8</v>
+      <c r="W31" s="15" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="X31" s="3" t="n">
+        <v>77.8</v>
       </c>
       <c r="Y31" s="3" t="n">
         <v>6.5</v>
@@ -3104,44 +3109,44 @@
       <c r="C32" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="D32" s="15" t="n">
-        <v>23.28</v>
-      </c>
-      <c r="E32" s="15" t="n">
+      <c r="D32" s="3" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="E32" s="14" t="n">
         <v>4.5</v>
       </c>
-      <c r="F32" s="15" t="n">
+      <c r="F32" s="14" t="n">
         <v>35</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>9.4</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K32" s="3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K32" s="9" t="n">
         <v>22.5</v>
       </c>
       <c r="L32" s="13" t="inlineStr"/>
       <c r="M32" s="3" t="n">
-        <v>18.1</v>
+        <v>18.7</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="Q32" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q32" s="9" t="n">
         <v>29.9</v>
       </c>
       <c r="R32" s="3" t="n">
@@ -3151,24 +3156,26 @@
         <v>26.8</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>3.5</v>
+        <v>35.8</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="V32" s="15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W32" s="11" t="n">
+      <c r="V32" s="9" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="W32" s="9" t="n">
         <v>25.8</v>
       </c>
-      <c r="X32" s="3" t="n">
-        <v>85.3</v>
-      </c>
-      <c r="Y32" s="3" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="Z32" s="3" t="inlineStr"/>
+      <c r="X32" s="9" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="Y32" s="9" t="n">
+        <v>124.2</v>
+      </c>
+      <c r="Z32" s="9" t="n">
+        <v>-6.5</v>
+      </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -3183,19 +3190,19 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D33" s="15" t="n">
-        <v>92.59999999999999</v>
-      </c>
-      <c r="E33" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D33" s="9" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="E33" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="F33" s="15" t="n">
-        <v>2.5</v>
+      <c r="F33" s="9" t="n">
+        <v>25.3</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>1.4</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>17.9</v>
@@ -3206,51 +3213,51 @@
       <c r="J33" s="3" t="n">
         <v>4.5</v>
       </c>
-      <c r="K33" s="3" t="n">
+      <c r="K33" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="M33" s="15" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="M33" s="14" t="n">
         <v>1.8</v>
       </c>
       <c r="N33" s="3" t="inlineStr"/>
       <c r="O33" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P33" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" s="3" t="n">
+      <c r="Q33" s="9" t="n">
         <v>28.9</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>24.8</v>
+        <v>27.8</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>7.8</v>
+        <v>78.2</v>
       </c>
       <c r="U33" s="3" t="n">
         <v>24.2</v>
       </c>
-      <c r="V33" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="W33" s="11" t="n">
+      <c r="V33" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="W33" s="9" t="n">
         <v>27.4</v>
       </c>
-      <c r="X33" s="3" t="n">
-        <v>80.3</v>
-      </c>
-      <c r="Y33" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Z33" s="3" t="n">
-        <v>15</v>
+      <c r="X33" s="9" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="Y33" s="9" t="n">
+        <v>138.1</v>
+      </c>
+      <c r="Z33" s="9" t="n">
+        <v>-10.1</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3265,20 +3272,22 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr"/>
-      <c r="D34" s="11" t="n">
+      <c r="C34" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D34" s="9" t="n">
         <v>32.2</v>
       </c>
-      <c r="E34" s="11" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="F34" s="11" t="n">
+      <c r="E34" s="9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="F34" s="9" t="n">
         <v>25.8</v>
       </c>
-      <c r="G34" s="11" t="n">
+      <c r="G34" s="9" t="n">
         <v>12.7</v>
       </c>
-      <c r="H34" s="17" t="n">
+      <c r="H34" s="3" t="n">
         <v>18</v>
       </c>
       <c r="I34" s="3" t="n">
@@ -3287,26 +3296,26 @@
       <c r="J34" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K34" s="3" t="n">
+      <c r="K34" s="9" t="n">
         <v>13.5</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="M34" s="15" t="n">
+      <c r="M34" s="14" t="n">
         <v>1.9</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>8.1</v>
+        <v>87.2</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="Q34" s="3" t="n">
-        <v>27.8</v>
+        <v>1.2</v>
+      </c>
+      <c r="Q34" s="9" t="n">
+        <v>24.8</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>20.9</v>
@@ -3315,25 +3324,25 @@
         <v>22.3</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>61.2</v>
+        <v>67.2</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="V34" s="3" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="V34" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="W34" s="11" t="n">
+      <c r="W34" s="9" t="n">
         <v>21.5</v>
       </c>
-      <c r="X34" s="3" t="n">
-        <v>86.3</v>
-      </c>
-      <c r="Y34" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="Z34" s="3" t="n">
-        <v>9</v>
+      <c r="X34" s="9" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="Y34" s="9" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="Z34" s="9" t="n">
+        <v>-2.3</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3349,18 +3358,18 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D35" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D35" s="9" t="n">
         <v>30.4</v>
       </c>
-      <c r="E35" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="G35" s="3" t="n">
+      <c r="E35" s="9" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F35" s="9" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="G35" s="9" t="n">
         <v>12</v>
       </c>
       <c r="H35" s="3" t="n">
@@ -3372,25 +3381,25 @@
       <c r="J35" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="K35" s="3" t="n">
+      <c r="K35" s="9" t="n">
         <v>1.6</v>
       </c>
       <c r="L35" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="M35" s="15" t="n">
-        <v>1.3</v>
+      <c r="M35" s="14" t="n">
+        <v>1.8</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>92.40000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q35" s="9" t="n">
         <v>28</v>
       </c>
       <c r="R35" s="3" t="n">
@@ -3400,25 +3409,25 @@
         <v>24.6</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>129.2</v>
+        <v>15.2</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V35" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="W35" s="11" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="V35" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="W35" s="9" t="n">
         <v>24.2</v>
       </c>
-      <c r="X35" s="3" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="Y35" s="3" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="Z35" s="3" t="n">
-        <v>33.6</v>
+      <c r="X35" s="9" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="Y35" s="9" t="n">
+        <v>114.2</v>
+      </c>
+      <c r="Z35" s="9" t="n">
+        <v>-3.8</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3434,8 +3443,8 @@
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr"/>
-      <c r="D36" s="17" t="n">
-        <v>33.6</v>
+      <c r="D36" s="14" t="n">
+        <v>93.59999999999999</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>19</v>
@@ -3455,53 +3464,53 @@
       <c r="J36" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="K36" s="3" t="n">
+      <c r="K36" s="9" t="n">
         <v>11.5</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="M36" s="15" t="n">
+      <c r="M36" s="14" t="n">
         <v>1.8</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>90.2</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q36" s="9" t="n">
         <v>31.2</v>
       </c>
-      <c r="R36" s="17" t="n">
-        <v>35</v>
+      <c r="R36" s="3" t="n">
+        <v>25</v>
       </c>
       <c r="S36" s="3" t="n">
         <v>27.9</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>48.2</v>
+        <v>4.4</v>
       </c>
       <c r="U36" s="3" t="n">
         <v>28.3</v>
       </c>
-      <c r="V36" s="3" t="n">
+      <c r="V36" s="9" t="n">
         <v>23.9</v>
       </c>
-      <c r="W36" s="11" t="n">
+      <c r="W36" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="X36" s="3" t="n">
-        <v>85.2</v>
-      </c>
-      <c r="Y36" s="3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Z36" s="3" t="n">
-        <v>17.6</v>
+      <c r="X36" s="9" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="Y36" s="9" t="n">
+        <v>120.3</v>
+      </c>
+      <c r="Z36" s="9" t="n">
+        <v>-6</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3517,13 +3526,13 @@
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr"/>
-      <c r="D37" s="18" t="n">
+      <c r="D37" s="9" t="n">
         <v>161.5</v>
       </c>
-      <c r="E37" s="18" t="n">
-        <v>1929.5</v>
-      </c>
-      <c r="F37" s="18" t="n">
+      <c r="E37" s="15" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="F37" s="9" t="n">
         <v>126.9</v>
       </c>
       <c r="G37" s="3" t="n">
@@ -3538,53 +3547,53 @@
       <c r="J37" s="3" t="n">
         <v>20.3</v>
       </c>
-      <c r="K37" s="18" t="n">
-        <v>949.9</v>
-      </c>
-      <c r="L37" s="18" t="n">
-        <v>951.1</v>
-      </c>
-      <c r="M37" s="18" t="n">
-        <v>0.1</v>
+      <c r="K37" s="9" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="L37" s="15" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="M37" s="15" t="n">
+        <v>2.1</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>11.7</v>
+        <v>1.1</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>150.2</v>
+        <v>50.2</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="Q37" s="18" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q37" s="9" t="n">
         <v>142.8</v>
       </c>
-      <c r="R37" s="18" t="n">
-        <v>117.3</v>
+      <c r="R37" s="15" t="n">
+        <v>17.5</v>
       </c>
       <c r="S37" s="3" t="n">
         <v>120.4</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>101.3</v>
+        <v>70.3</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>124.7</v>
       </c>
-      <c r="V37" s="18" t="n">
-        <v>111</v>
-      </c>
-      <c r="W37" s="11" t="n">
+      <c r="V37" s="9" t="n">
+        <v>110.1</v>
+      </c>
+      <c r="W37" s="9" t="n">
         <v>125.9</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>7367.2</v>
+        <v>267.2</v>
       </c>
       <c r="Y37" s="3" t="n">
         <v>37.2</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>247.3</v>
+        <v>24.7</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3600,14 +3609,14 @@
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr"/>
-      <c r="D38" s="18" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="E38" s="18" t="n">
+      <c r="D38" s="14" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="E38" s="15" t="n">
         <v>18.4</v>
       </c>
       <c r="F38" s="15" t="n">
-        <v>2.5</v>
+        <v>25.5</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>13.9</v>
@@ -3621,26 +3630,28 @@
       <c r="J38" s="3" t="n">
         <v>4.1</v>
       </c>
-      <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="18" t="n">
-        <v>14</v>
-      </c>
-      <c r="M38" s="18" t="n">
-        <v>17.8</v>
+      <c r="K38" s="3" t="n">
+        <v>555.5</v>
+      </c>
+      <c r="L38" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="M38" s="15" t="n">
+        <v>7.8</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>18.8</v>
+        <v>1.5</v>
       </c>
       <c r="O38" s="3" t="n">
         <v>90.90000000000001</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Q38" s="18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Q38" s="9" t="n">
         <v>28.6</v>
       </c>
-      <c r="R38" s="18" t="n">
+      <c r="R38" s="15" t="n">
         <v>23.5</v>
       </c>
       <c r="S38" s="3" t="n">
@@ -3652,20 +3663,20 @@
       <c r="U38" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="V38" s="18" t="n">
-        <v>82.2</v>
-      </c>
-      <c r="W38" s="11" t="n">
+      <c r="V38" s="9" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="W38" s="9" t="n">
         <v>25.2</v>
       </c>
-      <c r="X38" s="3" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="Y38" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z38" s="3" t="n">
-        <v>14.9</v>
+      <c r="X38" s="9" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="Y38" s="9" t="n">
+        <v>119.8</v>
+      </c>
+      <c r="Z38" s="9" t="n">
+        <v>-5.3</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3684,7 +3695,7 @@
       <c r="D39" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="E39" s="15" t="n">
+      <c r="E39" s="14" t="n">
         <v>45.3</v>
       </c>
       <c r="F39" s="3" t="n">
@@ -3693,7 +3704,7 @@
       <c r="G39" s="3" t="n">
         <v>45.4</v>
       </c>
-      <c r="H39" s="17" t="n">
+      <c r="H39" s="3" t="n">
         <v>17</v>
       </c>
       <c r="I39" s="3" t="n">
@@ -3702,18 +3713,18 @@
       <c r="J39" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="K39" s="3" t="n">
-        <v>60.2</v>
-      </c>
-      <c r="L39" s="15" t="n">
-        <v>49</v>
+      <c r="K39" s="9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>19.8</v>
+        <v>18</v>
       </c>
       <c r="N39" s="3" t="inlineStr"/>
       <c r="O39" s="3" t="n">
-        <v>79.59999999999999</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>0</v>
@@ -3725,7 +3736,7 @@
         <v>22.6</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>22.1</v>
+        <v>23.1</v>
       </c>
       <c r="T39" s="3" t="n">
         <v>61.2</v>
@@ -3736,14 +3747,14 @@
       <c r="V39" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="W39" s="15" t="n">
-        <v>2.4</v>
+      <c r="W39" s="14" t="n">
+        <v>24.17</v>
       </c>
       <c r="X39" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z39" s="3" t="n">
         <v>22</v>
@@ -3764,38 +3775,38 @@
       <c r="C40" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="D40" s="11" t="n">
+      <c r="D40" s="9" t="n">
         <v>32.5</v>
       </c>
-      <c r="E40" s="11" t="n">
+      <c r="E40" s="9" t="n">
         <v>18.3</v>
       </c>
-      <c r="F40" s="11" t="n">
+      <c r="F40" s="9" t="n">
         <v>25.4</v>
       </c>
-      <c r="G40" s="11" t="n">
+      <c r="G40" s="9" t="n">
         <v>14.2</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>18.8</v>
+        <v>18</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>2.9</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="K40" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K40" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="M40" s="15" t="n">
-        <v>1.8</v>
+      <c r="M40" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>92.2</v>
@@ -3804,7 +3815,7 @@
         <v>0.2</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>21.8</v>
+        <v>21.2</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>28.2</v>
@@ -3816,22 +3827,22 @@
         <v>47.2</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="V40" s="11" t="n">
-        <v>94.3</v>
-      </c>
-      <c r="W40" s="11" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="X40" s="11" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="Y40" s="11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="V40" s="3" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="W40" s="3" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="X40" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="Y40" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Z40" s="11" t="n">
-        <v>826.2</v>
+      <c r="Z40" s="3" t="n">
+        <v>2.5</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3847,16 +3858,16 @@
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr"/>
-      <c r="D41" s="11" t="n">
+      <c r="D41" s="9" t="n">
         <v>31.8</v>
       </c>
-      <c r="E41" s="11" t="n">
+      <c r="E41" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="F41" s="11" t="n">
+      <c r="F41" s="9" t="n">
         <v>25.4</v>
       </c>
-      <c r="G41" s="11" t="n">
+      <c r="G41" s="9" t="n">
         <v>12.8</v>
       </c>
       <c r="H41" s="3" t="n">
@@ -3866,26 +3877,26 @@
         <v>0.3</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K41" s="3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K41" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="17" t="n">
-        <v>9.1</v>
+      <c r="L41" s="3" t="n">
+        <v>20.1</v>
       </c>
       <c r="M41" s="3" t="n">
         <v>20</v>
       </c>
       <c r="N41" s="3" t="inlineStr"/>
       <c r="O41" s="3" t="n">
-        <v>81.2</v>
+        <v>91.2</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>1.6</v>
+        <v>0.2</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>29.4</v>
+        <v>24.1</v>
       </c>
       <c r="R41" s="3" t="n">
         <v>22.8</v>
@@ -3894,7 +3905,7 @@
         <v>27</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>37.8</v>
+        <v>59.2</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>9</v>
@@ -3912,7 +3923,7 @@
         <v>2.6</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3939,25 +3950,25 @@
         <v>25.6</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>1.3</v>
+        <v>13.5</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="J42" s="17" t="n">
-        <v>72.8</v>
-      </c>
-      <c r="K42" s="3" t="n">
+      <c r="J42" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="K42" s="9" t="n">
         <v>1.5</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>18.4</v>
+        <v>19.4</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>13.3</v>
+        <v>19.3</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="O42" s="3" t="n">
         <v>92.2</v>
@@ -3965,26 +3976,26 @@
       <c r="P42" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q42" s="15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R42" s="15" t="n">
-        <v>82</v>
+      <c r="Q42" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>22</v>
       </c>
       <c r="S42" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>11.6</v>
+        <v>14.5</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="V42" s="15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V42" s="14" t="n">
         <v>2.2</v>
       </c>
-      <c r="W42" s="15" t="n">
-        <v>0.7</v>
+      <c r="W42" s="3" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="X42" s="3" t="inlineStr"/>
       <c r="Y42" s="3" t="inlineStr"/>
@@ -4012,7 +4023,7 @@
       <c r="H43" s="3" t="inlineStr"/>
       <c r="I43" s="3" t="inlineStr"/>
       <c r="J43" s="3" t="inlineStr"/>
-      <c r="K43" s="13" t="inlineStr"/>
+      <c r="K43" s="9" t="inlineStr"/>
       <c r="L43" s="13" t="inlineStr"/>
       <c r="M43" s="13" t="inlineStr"/>
       <c r="N43" s="3" t="inlineStr"/>
@@ -4051,7 +4062,7 @@
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr"/>
-      <c r="K44" s="13" t="inlineStr"/>
+      <c r="K44" s="9" t="inlineStr"/>
       <c r="L44" s="13" t="inlineStr"/>
       <c r="M44" s="13" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr"/>
@@ -4081,16 +4092,16 @@
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr"/>
-      <c r="D45" s="18" t="n">
-        <v>122.3</v>
-      </c>
-      <c r="E45" s="18" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="F45" s="18" t="n">
+      <c r="D45" s="9" t="n">
+        <v>129.4</v>
+      </c>
+      <c r="E45" s="9" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="F45" s="9" t="n">
         <v>102</v>
       </c>
-      <c r="G45" s="3" t="n">
+      <c r="G45" s="9" t="n">
         <v>54.7</v>
       </c>
       <c r="H45" s="3" t="n">
@@ -4100,50 +4111,50 @@
         <v>9.1</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K45" s="18" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="L45" s="18" t="n">
-        <v>111.4</v>
-      </c>
-      <c r="M45" s="18" t="n">
-        <v>111.9</v>
+        <v>15.6</v>
+      </c>
+      <c r="K45" s="9" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="L45" s="15" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="M45" s="15" t="n">
+        <v>11.2</v>
       </c>
       <c r="N45" s="3" t="inlineStr"/>
       <c r="O45" s="3" t="n">
-        <v>2366.2</v>
+        <v>26.6</v>
       </c>
       <c r="P45" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q45" s="18" t="n">
-        <v>106.9</v>
-      </c>
-      <c r="R45" s="18" t="n">
+      <c r="Q45" s="15" t="n">
+        <v>106.7</v>
+      </c>
+      <c r="R45" s="15" t="n">
         <v>102.7</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>241.2</v>
+        <v>241.8</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>132.7</v>
+        <v>38.7</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V45" s="18" t="n">
-        <v>892.7</v>
-      </c>
-      <c r="W45" s="18" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="V45" s="15" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="W45" s="15" t="n">
         <v>96.3</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>19327.2</v>
+        <v>232.7</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>21.4</v>
+        <v>21.7</v>
       </c>
       <c r="Z45" s="3" t="n">
         <v>8.199999999999999</v>
@@ -4162,14 +4173,14 @@
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr"/>
-      <c r="D46" s="15" t="n">
+      <c r="D46" s="14" t="n">
         <v>1.1</v>
       </c>
-      <c r="E46" s="18" t="n">
+      <c r="E46" s="15" t="n">
         <v>32.3</v>
       </c>
       <c r="F46" s="15" t="n">
-        <v>1.8</v>
+        <v>18.7</v>
       </c>
       <c r="G46" s="3" t="n">
         <v>25.5</v>
@@ -4178,56 +4189,56 @@
         <v>17.5</v>
       </c>
       <c r="I46" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L46" s="15" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="M46" s="15" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O46" s="3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="P46" s="3" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="Q46" s="15" t="n">
         <v>0.2</v>
       </c>
-      <c r="J46" s="17" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="K46" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L46" s="18" t="n">
-        <v>92.40000000000001</v>
-      </c>
-      <c r="M46" s="18" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="N46" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="O46" s="3" t="n">
-        <v>92.3</v>
-      </c>
-      <c r="P46" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q46" s="18" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R46" s="18" t="n">
+      <c r="R46" s="15" t="n">
         <v>25.7</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>22.9</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="V46" s="18" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="V46" s="15" t="n">
         <v>21.4</v>
       </c>
-      <c r="W46" s="18" t="n">
-        <v>2.4</v>
+      <c r="W46" s="15" t="n">
+        <v>24.1</v>
       </c>
       <c r="X46" s="3" t="n">
         <v>60.2</v>
       </c>
       <c r="Y46" s="3" t="inlineStr"/>
       <c r="Z46" s="3" t="n">
-        <v>992.9</v>
+        <v>2.2</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_recalcmultiday.xlsx
+++ b/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_recalcmultiday.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF9933"/>
-        <bgColor rgb="00FF9933"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -137,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -155,25 +149,22 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -787,16 +778,16 @@
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr"/>
-      <c r="D4" s="9" t="n">
+      <c r="D4" s="8" t="n">
         <v>31.7</v>
       </c>
-      <c r="E4" s="9" t="n">
+      <c r="E4" s="8" t="n">
         <v>16.9</v>
       </c>
-      <c r="F4" s="9" t="n">
+      <c r="F4" s="8" t="n">
         <v>24.3</v>
       </c>
-      <c r="G4" s="9" t="n">
+      <c r="G4" s="8" t="n">
         <v>14.8</v>
       </c>
       <c r="H4" s="3" t="n">
@@ -811,49 +802,49 @@
       <c r="K4" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="L4" s="9" t="n">
+      <c r="L4" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="M4" s="9" t="n">
+      <c r="M4" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="N4" s="9" t="n">
+      <c r="N4" s="8" t="n">
         <v>21.2</v>
       </c>
-      <c r="O4" s="9" t="n">
+      <c r="O4" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="P4" s="9" t="n">
+      <c r="P4" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" s="9" t="n">
+      <c r="Q4" s="8" t="n">
         <v>30.6</v>
       </c>
-      <c r="R4" s="9" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="S4" s="9" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="T4" s="9" t="n">
-        <v>67.09999999999999</v>
-      </c>
-      <c r="U4" s="9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="V4" s="9" t="n">
+      <c r="R4" s="3" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="V4" s="8" t="n">
         <v>27.5</v>
       </c>
-      <c r="W4" s="9" t="n">
+      <c r="W4" s="8" t="n">
         <v>24.9</v>
       </c>
-      <c r="X4" s="9" t="n">
+      <c r="X4" s="8" t="n">
         <v>31.5</v>
       </c>
-      <c r="Y4" s="9" t="n">
+      <c r="Y4" s="8" t="n">
         <v>85.7</v>
       </c>
-      <c r="Z4" s="9" t="n">
+      <c r="Z4" s="8" t="n">
         <v>5.2</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
@@ -870,16 +861,16 @@
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="8" t="n">
         <v>26.2</v>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E5" s="8" t="n">
         <v>17.4</v>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="F5" s="8" t="n">
         <v>21.8</v>
       </c>
-      <c r="G5" s="9" t="n">
+      <c r="G5" s="8" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="H5" s="3" t="n">
@@ -894,49 +885,49 @@
       <c r="K5" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L5" s="9" t="n">
+      <c r="L5" s="8" t="n">
         <v>17.6</v>
       </c>
-      <c r="M5" s="9" t="n">
+      <c r="M5" s="8" t="n">
         <v>17.6</v>
       </c>
-      <c r="N5" s="9" t="n">
+      <c r="N5" s="8" t="n">
         <v>20.1</v>
       </c>
-      <c r="O5" s="9" t="n">
+      <c r="O5" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="P5" s="9" t="n">
+      <c r="P5" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" s="9" t="n">
+      <c r="Q5" s="8" t="n">
         <v>23.9</v>
       </c>
-      <c r="R5" s="9" t="n">
+      <c r="R5" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="S5" s="9" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="T5" s="9" t="n">
-        <v>83.8</v>
-      </c>
-      <c r="U5" s="9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="V5" s="9" t="n">
+      <c r="S5" s="3" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="T5" s="3" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="U5" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="V5" s="8" t="n">
         <v>23.1</v>
       </c>
-      <c r="W5" s="9" t="n">
+      <c r="W5" s="8" t="n">
         <v>21.3</v>
       </c>
-      <c r="X5" s="9" t="n">
+      <c r="X5" s="8" t="n">
         <v>25.3</v>
       </c>
-      <c r="Y5" s="9" t="n">
+      <c r="Y5" s="8" t="n">
         <v>89.59999999999999</v>
       </c>
-      <c r="Z5" s="9" t="n">
+      <c r="Z5" s="8" t="n">
         <v>2.9</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -953,16 +944,16 @@
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr"/>
-      <c r="D6" s="9" t="n">
+      <c r="D6" s="8" t="n">
         <v>32.2</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" s="8" t="n">
         <v>24.6</v>
       </c>
-      <c r="G6" s="9" t="n">
+      <c r="G6" s="8" t="n">
         <v>15.2</v>
       </c>
       <c r="H6" s="3" t="n">
@@ -975,51 +966,51 @@
         <v>4.4</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="L6" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="L6" s="8" t="n">
         <v>17.4</v>
       </c>
-      <c r="M6" s="9" t="n">
+      <c r="M6" s="8" t="n">
         <v>17.5</v>
       </c>
-      <c r="N6" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="O6" s="9" t="n">
-        <v>100.6</v>
-      </c>
-      <c r="P6" s="9" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="Q6" s="9" t="n">
+      <c r="N6" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="8" t="n">
         <v>29.5</v>
       </c>
-      <c r="R6" s="9" t="n">
+      <c r="R6" s="3" t="n">
         <v>24.1</v>
       </c>
-      <c r="S6" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="T6" s="9" t="n">
-        <v>72.8</v>
-      </c>
-      <c r="U6" s="9" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="V6" s="9" t="n">
+      <c r="S6" s="3" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="U6" s="3" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="V6" s="8" t="n">
         <v>27.2</v>
       </c>
-      <c r="W6" s="9" t="n">
+      <c r="W6" s="8" t="n">
         <v>22.6</v>
       </c>
-      <c r="X6" s="9" t="n">
+      <c r="X6" s="8" t="n">
         <v>27.4</v>
       </c>
-      <c r="Y6" s="9" t="n">
+      <c r="Y6" s="8" t="n">
         <v>76</v>
       </c>
-      <c r="Z6" s="9" t="n">
+      <c r="Z6" s="8" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
@@ -1036,16 +1027,16 @@
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="9" t="n">
+      <c r="D7" s="8" t="n">
         <v>30.5</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F7" s="8" t="n">
         <v>25.2</v>
       </c>
-      <c r="G7" s="9" t="n">
+      <c r="G7" s="8" t="n">
         <v>10.6</v>
       </c>
       <c r="H7" s="3" t="n">
@@ -1060,49 +1051,49 @@
       <c r="K7" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="L7" s="9" t="n">
+      <c r="L7" s="8" t="n">
         <v>20.3</v>
       </c>
-      <c r="M7" s="9" t="n">
+      <c r="M7" s="8" t="n">
         <v>20.2</v>
       </c>
-      <c r="N7" s="9" t="n">
+      <c r="N7" s="8" t="n">
         <v>23.7</v>
       </c>
-      <c r="O7" s="9" t="n">
+      <c r="O7" s="8" t="n">
         <v>99.40000000000001</v>
       </c>
-      <c r="P7" s="9" t="n">
+      <c r="P7" s="8" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q7" s="9" t="n">
+      <c r="Q7" s="8" t="n">
         <v>20.1</v>
       </c>
-      <c r="R7" s="9" t="n">
+      <c r="R7" s="8" t="n">
         <v>19.5</v>
       </c>
-      <c r="S7" s="9" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="T7" s="9" t="n">
-        <v>96.3</v>
-      </c>
-      <c r="U7" s="9" t="n">
+      <c r="S7" s="8" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="U7" s="8" t="n">
         <v>0.9</v>
       </c>
-      <c r="V7" s="9" t="n">
+      <c r="V7" s="8" t="n">
         <v>21.4</v>
       </c>
-      <c r="W7" s="9" t="n">
+      <c r="W7" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="X7" s="9" t="n">
+      <c r="X7" s="8" t="n">
         <v>24.3</v>
       </c>
-      <c r="Y7" s="9" t="n">
+      <c r="Y7" s="8" t="n">
         <v>95.2</v>
       </c>
-      <c r="Z7" s="9" t="n">
+      <c r="Z7" s="8" t="n">
         <v>1.2</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
@@ -1119,16 +1110,16 @@
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="9" t="n">
+      <c r="D8" s="8" t="n">
         <v>26.8</v>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="E8" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="F8" s="9" t="n">
+      <c r="F8" s="8" t="n">
         <v>22.6</v>
       </c>
-      <c r="G8" s="9" t="n">
+      <c r="G8" s="8" t="n">
         <v>8.4</v>
       </c>
       <c r="H8" s="3" t="n">
@@ -1143,49 +1134,49 @@
       <c r="K8" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="L8" s="9" t="n">
+      <c r="L8" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="M8" s="9" t="n">
+      <c r="M8" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="N8" s="9" t="n">
+      <c r="N8" s="8" t="n">
         <v>21.8</v>
       </c>
-      <c r="O8" s="9" t="n">
+      <c r="O8" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="P8" s="9" t="n">
+      <c r="P8" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" s="9" t="n">
+      <c r="Q8" s="8" t="n">
         <v>25.8</v>
       </c>
-      <c r="R8" s="9" t="n">
+      <c r="R8" s="3" t="n">
         <v>22.3</v>
       </c>
-      <c r="S8" s="9" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="T8" s="9" t="n">
-        <v>81</v>
-      </c>
-      <c r="U8" s="9" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="V8" s="9" t="n">
+      <c r="S8" s="3" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="U8" s="3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="V8" s="8" t="n">
         <v>24.6</v>
       </c>
-      <c r="W8" s="9" t="n">
+      <c r="W8" s="8" t="n">
         <v>21.4</v>
       </c>
-      <c r="X8" s="9" t="n">
+      <c r="X8" s="8" t="n">
         <v>25.5</v>
       </c>
-      <c r="Y8" s="9" t="n">
+      <c r="Y8" s="8" t="n">
         <v>82.40000000000001</v>
       </c>
-      <c r="Z8" s="9" t="n">
+      <c r="Z8" s="8" t="n">
         <v>5.5</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
@@ -1202,16 +1193,16 @@
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="9" t="n">
+      <c r="D9" s="8" t="n">
         <v>147.4</v>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" s="8" t="n">
         <v>89.59999999999999</v>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="8" t="n">
         <v>118.5</v>
       </c>
-      <c r="G9" s="9" t="n">
+      <c r="G9" s="8" t="n">
         <v>57.8</v>
       </c>
       <c r="H9" s="3" t="n">
@@ -1221,15 +1212,15 @@
         <v>9.6</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="K9" s="15" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="K9" s="14" t="n">
         <v>44.1</v>
       </c>
-      <c r="L9" s="9" t="n">
+      <c r="L9" s="8" t="n">
         <v>92.59999999999999</v>
       </c>
-      <c r="M9" s="9" t="n">
+      <c r="M9" s="8" t="n">
         <v>92.59999999999999</v>
       </c>
       <c r="N9" s="3" t="n">
@@ -1241,11 +1232,11 @@
       <c r="P9" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q9" s="9" t="n">
+      <c r="Q9" s="8" t="n">
         <v>129.9</v>
       </c>
-      <c r="R9" s="9" t="n">
-        <v>110.7</v>
+      <c r="R9" s="14" t="n">
+        <v>110.1</v>
       </c>
       <c r="S9" s="3" t="n">
         <v>122.3</v>
@@ -1256,10 +1247,10 @@
       <c r="U9" s="3" t="n">
         <v>48.8</v>
       </c>
-      <c r="V9" s="9" t="n">
+      <c r="V9" s="8" t="n">
         <v>123.8</v>
       </c>
-      <c r="W9" s="9" t="n">
+      <c r="W9" s="8" t="n">
         <v>110.8</v>
       </c>
       <c r="X9" s="3" t="n">
@@ -1285,20 +1276,20 @@
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr"/>
-      <c r="D10" s="9" t="n">
+      <c r="D10" s="8" t="n">
         <v>29.5</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E10" s="8" t="n">
         <v>17.9</v>
       </c>
-      <c r="F10" s="9" t="n">
+      <c r="F10" s="8" t="n">
         <v>23.7</v>
       </c>
-      <c r="G10" s="9" t="n">
-        <v>11.6</v>
+      <c r="G10" s="3" t="n">
+        <v>19.6</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>1.9</v>
@@ -1309,49 +1300,49 @@
       <c r="K10" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L10" s="9" t="n">
+      <c r="L10" s="8" t="n">
         <v>18.5</v>
       </c>
-      <c r="M10" s="9" t="n">
+      <c r="M10" s="8" t="n">
         <v>18.5</v>
       </c>
-      <c r="N10" s="9" t="n">
+      <c r="N10" s="8" t="n">
         <v>21.3</v>
       </c>
-      <c r="O10" s="9" t="n">
+      <c r="O10" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="P10" s="9" t="n">
+      <c r="P10" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" s="9" t="n">
+      <c r="Q10" s="8" t="n">
         <v>25.9</v>
       </c>
-      <c r="R10" s="9" t="n">
+      <c r="R10" s="14" t="n">
         <v>22</v>
       </c>
-      <c r="S10" s="9" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="T10" s="9" t="n">
-        <v>79.09999999999999</v>
-      </c>
-      <c r="U10" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="V10" s="9" t="n">
+      <c r="S10" s="3" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="T10" s="3" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="U10" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="V10" s="8" t="n">
         <v>24.8</v>
       </c>
-      <c r="W10" s="9" t="n">
+      <c r="W10" s="8" t="n">
         <v>22.2</v>
       </c>
-      <c r="X10" s="9" t="n">
+      <c r="X10" s="8" t="n">
         <v>26.8</v>
       </c>
-      <c r="Y10" s="9" t="n">
+      <c r="Y10" s="8" t="n">
         <v>85.5</v>
       </c>
-      <c r="Z10" s="9" t="n">
+      <c r="Z10" s="8" t="n">
         <v>4.5</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
@@ -1368,21 +1359,21 @@
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="9" t="n">
-        <v>29</v>
-      </c>
-      <c r="E11" s="9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="F11" s="9" t="n">
+      <c r="D11" s="8" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="F11" s="8" t="n">
         <v>23.8</v>
       </c>
-      <c r="G11" s="9" t="n">
+      <c r="G11" s="8" t="n">
         <v>10.5</v>
       </c>
       <c r="H11" s="3" t="inlineStr"/>
       <c r="I11" s="3" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J11" s="3" t="inlineStr"/>
       <c r="K11" s="3" t="inlineStr"/>
@@ -1401,25 +1392,25 @@
       <c r="P11" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" s="9" t="n">
+      <c r="Q11" s="8" t="n">
         <v>28.4</v>
       </c>
-      <c r="R11" s="9" t="n">
+      <c r="R11" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="S11" s="9" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="T11" s="9" t="n">
-        <v>76.2</v>
-      </c>
-      <c r="U11" s="9" t="n">
-        <v>9.199999999999999</v>
+      <c r="S11" s="3" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="T11" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="U11" s="3" t="n">
+        <v>12</v>
       </c>
       <c r="V11" s="3" t="n">
         <v>28.9</v>
       </c>
-      <c r="W11" s="9" t="n">
+      <c r="W11" s="8" t="n">
         <v>22.9</v>
       </c>
       <c r="X11" s="3" t="n">
@@ -1445,17 +1436,17 @@
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr"/>
-      <c r="D12" s="9" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="E12" s="9" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="F12" s="9" t="n">
+      <c r="D12" s="8" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F12" s="8" t="n">
         <v>22.4</v>
       </c>
-      <c r="G12" s="9" t="n">
-        <v>8.1</v>
+      <c r="G12" s="3" t="n">
+        <v>28.1</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>17.5</v>
@@ -1476,7 +1467,7 @@
         <v>18.8</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>90.2</v>
@@ -1484,25 +1475,25 @@
       <c r="P12" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q12" s="9" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="R12" s="9" t="n">
+      <c r="Q12" s="8" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="R12" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="S12" s="9" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="T12" s="9" t="n">
-        <v>87</v>
-      </c>
-      <c r="U12" s="9" t="n">
-        <v>3.9</v>
+      <c r="S12" s="3" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="T12" s="3" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="U12" s="3" t="n">
+        <v>5.2</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="W12" s="9" t="n">
+      <c r="W12" s="8" t="n">
         <v>21.1</v>
       </c>
       <c r="X12" s="3" t="n">
@@ -1528,16 +1519,16 @@
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr"/>
-      <c r="D13" s="9" t="n">
+      <c r="D13" s="8" t="n">
         <v>26.8</v>
       </c>
-      <c r="E13" s="9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="F13" s="9" t="n">
+      <c r="E13" s="8" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="F13" s="8" t="n">
         <v>22.7</v>
       </c>
-      <c r="G13" s="9" t="n">
+      <c r="G13" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="H13" s="3" t="n">
@@ -1559,7 +1550,7 @@
         <v>18.9</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>2.1</v>
+        <v>0.1</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>90.2</v>
@@ -1567,32 +1558,32 @@
       <c r="P13" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q13" s="9" t="n">
+      <c r="Q13" s="8" t="n">
         <v>22.2</v>
       </c>
-      <c r="R13" s="9" t="n">
+      <c r="R13" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="S13" s="9" t="n">
-        <v>24</v>
-      </c>
-      <c r="T13" s="9" t="n">
-        <v>89.5</v>
-      </c>
-      <c r="U13" s="9" t="n">
-        <v>2.8</v>
+      <c r="S13" s="3" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="T13" s="3" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="U13" s="3" t="n">
+        <v>3.8</v>
       </c>
       <c r="V13" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="W13" s="9" t="n">
+      <c r="W13" s="8" t="n">
         <v>20</v>
       </c>
       <c r="X13" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="Z13" s="3" t="n">
         <v>2.5</v>
@@ -1613,20 +1604,20 @@
       <c r="C14" s="3" t="n">
         <v>10.1</v>
       </c>
-      <c r="D14" s="9" t="n">
+      <c r="D14" s="8" t="n">
         <v>29.9</v>
       </c>
-      <c r="E14" s="9" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="F14" s="9" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="G14" s="9" t="n">
+      <c r="E14" s="8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="G14" s="8" t="n">
         <v>11.5</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>1.9</v>
@@ -1635,7 +1626,7 @@
         <v>2.7</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>22.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L14" s="3" t="n">
         <v>18.9</v>
@@ -1644,7 +1635,7 @@
         <v>18.7</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>91.2</v>
@@ -1652,32 +1643,32 @@
       <c r="P14" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q14" s="9" t="n">
+      <c r="Q14" s="8" t="n">
         <v>27.7</v>
       </c>
-      <c r="R14" s="9" t="n">
+      <c r="R14" s="3" t="n">
         <v>23.4</v>
       </c>
-      <c r="S14" s="9" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="T14" s="9" t="n">
-        <v>77.40000000000001</v>
-      </c>
-      <c r="U14" s="9" t="n">
-        <v>8.4</v>
+      <c r="S14" s="3" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="T14" s="3" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="U14" s="3" t="n">
+        <v>11</v>
       </c>
       <c r="V14" s="3" t="n">
         <v>25.1</v>
       </c>
-      <c r="W14" s="9" t="n">
+      <c r="W14" s="8" t="n">
         <v>22.8</v>
       </c>
       <c r="X14" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>77.2</v>
+        <v>74.2</v>
       </c>
       <c r="Z14" s="3" t="n">
         <v>5.4</v>
@@ -1696,23 +1687,23 @@
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr"/>
-      <c r="D15" s="9" t="n">
+      <c r="D15" s="8" t="n">
         <v>28.3</v>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="E15" s="8" t="n">
         <v>18.6</v>
       </c>
-      <c r="F15" s="9" t="n">
+      <c r="F15" s="8" t="n">
         <v>23.5</v>
       </c>
-      <c r="G15" s="9" t="n">
+      <c r="G15" s="8" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>2.7</v>
@@ -1727,7 +1718,7 @@
         <v>18.9</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>91.2</v>
@@ -1735,35 +1726,35 @@
       <c r="P15" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q15" s="9" t="n">
+      <c r="Q15" s="8" t="n">
         <v>26.6</v>
       </c>
-      <c r="R15" s="9" t="n">
+      <c r="R15" s="3" t="n">
         <v>22.9</v>
       </c>
-      <c r="S15" s="9" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="T15" s="9" t="n">
-        <v>80.2</v>
-      </c>
-      <c r="U15" s="9" t="n">
-        <v>6.9</v>
+      <c r="S15" s="3" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="T15" s="3" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="U15" s="3" t="n">
+        <v>9.1</v>
       </c>
       <c r="V15" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="W15" s="9" t="n">
+      <c r="W15" s="8" t="n">
         <v>20.9</v>
       </c>
       <c r="X15" s="3" t="n">
         <v>24.4</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>8.5</v>
+        <v>85.3</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1779,48 +1770,48 @@
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr"/>
-      <c r="D16" s="9" t="n">
+      <c r="D16" s="8" t="n">
         <v>140.4</v>
       </c>
-      <c r="E16" s="9" t="n">
-        <v>92.3</v>
-      </c>
-      <c r="F16" s="9" t="n">
-        <v>116.6</v>
+      <c r="E16" s="8" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>116.5</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>87.5</v>
+        <v>81.5</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="K16" s="12" t="inlineStr"/>
-      <c r="L16" s="15" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="K16" s="11" t="inlineStr"/>
+      <c r="L16" s="14" t="n">
         <v>95.3</v>
       </c>
-      <c r="M16" s="15" t="n">
+      <c r="M16" s="14" t="n">
         <v>94.59999999999999</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>1</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>53.2</v>
+        <v>153.2</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q16" s="9" t="n">
+      <c r="Q16" s="8" t="n">
         <v>129.2</v>
       </c>
-      <c r="R16" s="9" t="n">
-        <v>112.5</v>
+      <c r="R16" s="14" t="n">
+        <v>182.5</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>126.6</v>
@@ -1829,19 +1820,19 @@
         <v>38.2</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>49.2</v>
-      </c>
-      <c r="V16" s="15" t="n">
-        <v>114</v>
-      </c>
-      <c r="W16" s="9" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="V16" s="14" t="n">
+        <v>116.7</v>
+      </c>
+      <c r="W16" s="8" t="n">
         <v>107.7</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>124.6</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>408.9</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>15</v>
@@ -1860,18 +1851,18 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="D17" s="9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D17" s="8" t="n">
         <v>28.1</v>
       </c>
-      <c r="E17" s="9" t="n">
+      <c r="E17" s="8" t="n">
         <v>18.5</v>
       </c>
-      <c r="F17" s="9" t="n">
+      <c r="F17" s="8" t="n">
         <v>23.3</v>
       </c>
-      <c r="G17" s="9" t="n">
+      <c r="G17" s="8" t="n">
         <v>9.6</v>
       </c>
       <c r="H17" s="3" t="n">
@@ -1881,17 +1872,17 @@
         <v>1.9</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="15" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="M17" s="15" t="n">
-        <v>18.8</v>
+      <c r="L17" s="14" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="M17" s="14" t="n">
+        <v>18.9</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>2.2</v>
+        <v>22.1</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>91.2</v>
@@ -1899,29 +1890,29 @@
       <c r="P17" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q17" s="9" t="n">
+      <c r="Q17" s="8" t="n">
         <v>25.8</v>
       </c>
-      <c r="R17" s="9" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="S17" s="9" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="T17" s="9" t="n">
-        <v>82</v>
-      </c>
-      <c r="U17" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="V17" s="15" t="n">
+      <c r="R17" s="14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="S17" s="3" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="T17" s="3" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="U17" s="3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="V17" s="14" t="n">
         <v>22.9</v>
       </c>
-      <c r="W17" s="9" t="n">
+      <c r="W17" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="Y17" s="3" t="n">
         <v>82.2</v>
@@ -1943,20 +1934,20 @@
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr"/>
-      <c r="D18" s="9" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="E18" s="9" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="F18" s="9" t="n">
-        <v>22.3</v>
+      <c r="D18" s="8" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>19.5</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>12.4</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>15.5</v>
+        <v>16.6</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>2.1</v>
@@ -1964,17 +1955,17 @@
       <c r="J18" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="K18" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="9" t="n">
+      <c r="L18" s="8" t="n">
         <v>19.2</v>
       </c>
-      <c r="M18" s="14" t="n">
-        <v>1.1</v>
+      <c r="M18" s="8" t="n">
+        <v>19.6</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O18" s="3" t="n">
         <v>91.2</v>
@@ -1982,10 +1973,10 @@
       <c r="P18" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q18" s="14" t="n">
+      <c r="Q18" s="13" t="n">
         <v>89.2</v>
       </c>
-      <c r="R18" s="3" t="n">
+      <c r="R18" s="8" t="n">
         <v>23.2</v>
       </c>
       <c r="S18" s="3" t="n">
@@ -1995,10 +1986,10 @@
         <v>54.2</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="V18" s="9" t="n">
-        <v>21.8</v>
+        <v>10.1</v>
+      </c>
+      <c r="V18" s="13" t="n">
+        <v>12.18</v>
       </c>
       <c r="W18" s="3" t="n">
         <v>20.8</v>
@@ -2026,18 +2017,18 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D19" s="9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D19" s="8" t="n">
         <v>30.6</v>
       </c>
-      <c r="E19" s="9" t="n">
+      <c r="E19" s="8" t="n">
         <v>17.7</v>
       </c>
-      <c r="F19" s="9" t="n">
+      <c r="F19" s="8" t="n">
         <v>24.1</v>
       </c>
-      <c r="G19" s="9" t="n">
+      <c r="G19" s="8" t="n">
         <v>12.9</v>
       </c>
       <c r="H19" s="3" t="n">
@@ -2049,52 +2040,52 @@
       <c r="J19" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="K19" s="3" t="n">
+      <c r="K19" s="8" t="n">
         <v>27.9</v>
       </c>
-      <c r="L19" s="9" t="n">
+      <c r="L19" s="8" t="n">
         <v>18.3</v>
       </c>
-      <c r="M19" s="9" t="n">
+      <c r="M19" s="8" t="n">
         <v>18.2</v>
       </c>
-      <c r="N19" s="9" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="O19" s="9" t="n">
+      <c r="N19" s="8" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="O19" s="8" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="P19" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q19" s="8" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="R19" s="8" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="S19" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="T19" s="8" t="n">
         <v>99</v>
       </c>
-      <c r="P19" s="9" t="n">
+      <c r="U19" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q19" s="3" t="n">
+      <c r="V19" s="3" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="W19" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="R19" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="S19" s="3" t="n">
+      <c r="X19" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="T19" s="3" t="n">
-        <v>90.2</v>
-      </c>
-      <c r="U19" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="V19" s="9" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="W19" s="9" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="X19" s="9" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="Y19" s="9" t="n">
-        <v>97.5</v>
-      </c>
-      <c r="Z19" s="9" t="n">
+      <c r="Y19" s="3" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="Z19" s="3" t="n">
         <v>0.6</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
@@ -2111,19 +2102,19 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="D20" s="9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D20" s="8" t="n">
         <v>28.5</v>
       </c>
-      <c r="E20" s="9" t="n">
+      <c r="E20" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="F20" s="9" t="n">
+      <c r="F20" s="8" t="n">
         <v>23.7</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.9</v>
+        <v>29.6</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>17.6</v>
@@ -2132,49 +2123,49 @@
         <v>1.2</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K20" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K20" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L20" s="9" t="n">
+      <c r="L20" s="8" t="n">
         <v>19.2</v>
       </c>
-      <c r="M20" s="9" t="n">
+      <c r="M20" s="8" t="n">
         <v>19.2</v>
       </c>
-      <c r="N20" s="9" t="n">
+      <c r="N20" s="8" t="n">
         <v>22.2</v>
       </c>
-      <c r="O20" s="9" t="n">
+      <c r="O20" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="P20" s="9" t="n">
+      <c r="P20" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" s="14" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R20" s="3" t="n">
+      <c r="Q20" s="3" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="R20" s="8" t="n">
         <v>21.9</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>23.7</v>
+        <v>29.7</v>
       </c>
       <c r="T20" s="3" t="n">
         <v>72.2</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="V20" s="9" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="V20" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="W20" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>85.2</v>
+        <v>25.3</v>
       </c>
       <c r="Y20" s="3" t="n">
         <v>2.6</v>
@@ -2198,16 +2189,16 @@
       <c r="C21" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="D21" s="9" t="n">
+      <c r="D21" s="8" t="n">
         <v>28.4</v>
       </c>
-      <c r="E21" s="9" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="F21" s="9" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="G21" s="9" t="n">
+      <c r="E21" s="8" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="G21" s="3" t="n">
         <v>10.3</v>
       </c>
       <c r="H21" s="3" t="n">
@@ -2219,52 +2210,52 @@
       <c r="J21" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="K21" s="3" t="n">
+      <c r="K21" s="8" t="n">
         <v>3.8</v>
       </c>
-      <c r="L21" s="9" t="n">
+      <c r="L21" s="8" t="n">
         <v>19.4</v>
       </c>
-      <c r="M21" s="3" t="n">
+      <c r="M21" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="N21" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="O21" s="3" t="n">
-        <v>92.2</v>
-      </c>
-      <c r="P21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="3" t="n">
+      <c r="N21" s="8" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="O21" s="8" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="P21" s="8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q21" s="8" t="n">
         <v>19.2</v>
       </c>
-      <c r="R21" s="3" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="S21" s="3" t="n">
+      <c r="R21" s="8" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="S21" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="T21" s="3" t="n">
-        <v>88.2</v>
-      </c>
-      <c r="U21" s="3" t="n">
+      <c r="T21" s="8" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="U21" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="V21" s="9" t="n">
+      <c r="V21" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="W21" s="9" t="n">
+      <c r="W21" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="X21" s="9" t="n">
+      <c r="X21" s="3" t="n">
         <v>21.9</v>
       </c>
-      <c r="Y21" s="9" t="n">
-        <v>96.5</v>
-      </c>
-      <c r="Z21" s="9" t="n">
+      <c r="Y21" s="3" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="Z21" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
@@ -2281,18 +2272,18 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D22" s="9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D22" s="8" t="n">
         <v>29.2</v>
       </c>
-      <c r="E22" s="9" t="n">
+      <c r="E22" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="F22" s="9" t="n">
+      <c r="F22" s="8" t="n">
         <v>23.3</v>
       </c>
-      <c r="G22" s="9" t="n">
+      <c r="G22" s="8" t="n">
         <v>12.2</v>
       </c>
       <c r="H22" s="3" t="n">
@@ -2304,28 +2295,28 @@
       <c r="J22" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="K22" s="3" t="n">
+      <c r="K22" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="9" t="n">
+      <c r="L22" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="M22" s="9" t="n">
+      <c r="M22" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="N22" s="9" t="n">
+      <c r="N22" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="O22" s="9" t="n">
+      <c r="O22" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="P22" s="9" t="n">
+      <c r="P22" s="8" t="n">
         <v>0</v>
       </c>
       <c r="Q22" s="3" t="n">
         <v>28.5</v>
       </c>
-      <c r="R22" s="3" t="n">
+      <c r="R22" s="8" t="n">
         <v>23.1</v>
       </c>
       <c r="S22" s="3" t="n">
@@ -2335,9 +2326,9 @@
         <v>56.2</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="V22" s="9" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="V22" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="W22" s="3" t="n">
@@ -2366,16 +2357,16 @@
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr"/>
-      <c r="D23" s="9" t="n">
-        <v>142.6</v>
-      </c>
-      <c r="E23" s="9" t="n">
-        <v>90.40000000000001</v>
-      </c>
-      <c r="F23" s="9" t="n">
-        <v>116.5</v>
-      </c>
-      <c r="G23" s="9" t="n">
+      <c r="D23" s="8" t="n">
+        <v>142.5</v>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="F23" s="8" t="n">
+        <v>114</v>
+      </c>
+      <c r="G23" s="3" t="n">
         <v>52.2</v>
       </c>
       <c r="H23" s="3" t="n">
@@ -2387,48 +2378,48 @@
       <c r="J23" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="K23" s="15" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="L23" s="9" t="n">
+      <c r="K23" s="8" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="L23" s="8" t="n">
         <v>94.09999999999999</v>
       </c>
-      <c r="M23" s="15" t="n">
-        <v>92.90000000000001</v>
+      <c r="M23" s="8" t="n">
+        <v>93.40000000000001</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>2.1</v>
+        <v>8.1</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>458.2</v>
+        <v>451.2</v>
       </c>
       <c r="P23" s="3" t="inlineStr"/>
-      <c r="Q23" s="15" t="n">
+      <c r="Q23" s="14" t="n">
         <v>121</v>
       </c>
-      <c r="R23" s="15" t="n">
+      <c r="R23" s="8" t="n">
         <v>107.2</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>11.9</v>
+        <v>119.7</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>36</v>
+        <v>360.2</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>37.7</v>
-      </c>
-      <c r="V23" s="9" t="n">
-        <v>108.9</v>
-      </c>
-      <c r="W23" s="15" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="V23" s="14" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="W23" s="14" t="n">
         <v>102.6</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>117.7</v>
+        <v>117.8</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>27.6</v>
+        <v>427.6</v>
       </c>
       <c r="Z23" s="3" t="n">
         <v>12.7</v>
@@ -2449,50 +2440,50 @@
       <c r="C24" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D24" s="9" t="n">
+      <c r="D24" s="8" t="n">
         <v>28.5</v>
       </c>
-      <c r="E24" s="9" t="n">
+      <c r="E24" s="8" t="n">
         <v>17.1</v>
       </c>
-      <c r="F24" s="9" t="n">
+      <c r="F24" s="8" t="n">
         <v>22.8</v>
       </c>
-      <c r="G24" s="9" t="n">
+      <c r="G24" s="8" t="n">
         <v>11.4</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>0.2</v>
+        <v>1.5</v>
       </c>
       <c r="J24" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="K24" s="8" t="n">
-        <v>991999.1</v>
-      </c>
-      <c r="L24" s="9" t="n">
+      <c r="K24" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L24" s="8" t="n">
         <v>18.8</v>
       </c>
-      <c r="M24" s="9" t="n">
+      <c r="M24" s="8" t="n">
         <v>18.6</v>
       </c>
-      <c r="N24" s="9" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="O24" s="9" t="n">
-        <v>99.09999999999999</v>
-      </c>
-      <c r="P24" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q24" s="15" t="n">
+      <c r="N24" s="8" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="O24" s="8" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="P24" s="8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q24" s="14" t="n">
         <v>27.2</v>
       </c>
-      <c r="R24" s="15" t="n">
-        <v>2.4</v>
+      <c r="R24" s="8" t="n">
+        <v>21.4</v>
       </c>
       <c r="S24" s="3" t="n">
         <v>23.9</v>
@@ -2503,10 +2494,10 @@
       <c r="U24" s="3" t="n">
         <v>6.9</v>
       </c>
-      <c r="V24" s="9" t="n">
+      <c r="V24" s="14" t="n">
         <v>21.7</v>
       </c>
-      <c r="W24" s="15" t="n">
+      <c r="W24" s="14" t="n">
         <v>20.5</v>
       </c>
       <c r="X24" s="3" t="n">
@@ -2516,7 +2507,7 @@
         <v>2.5</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>8.5</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2532,23 +2523,23 @@
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr"/>
-      <c r="D25" s="9" t="n">
+      <c r="D25" s="8" t="n">
         <v>29.8</v>
       </c>
-      <c r="E25" s="9" t="n">
+      <c r="E25" s="8" t="n">
         <v>18.7</v>
       </c>
-      <c r="F25" s="9" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="G25" s="14" t="n">
+      <c r="F25" s="8" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="G25" s="13" t="n">
         <v>44.4</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>17.1</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>34.4</v>
@@ -2556,25 +2547,25 @@
       <c r="K25" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L25" s="9" t="n">
+      <c r="L25" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="M25" s="9" t="n">
+      <c r="M25" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="N25" s="9" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="O25" s="9" t="n">
-        <v>100</v>
-      </c>
-      <c r="P25" s="9" t="n">
+      <c r="N25" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="P25" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" s="14" t="n">
+      <c r="Q25" s="13" t="n">
         <v>2.6</v>
       </c>
-      <c r="R25" s="14" t="n">
+      <c r="R25" s="13" t="n">
         <v>3</v>
       </c>
       <c r="S25" s="3" t="n">
@@ -2589,11 +2580,11 @@
       <c r="V25" s="3" t="n">
         <v>25.3</v>
       </c>
-      <c r="W25" s="14" t="n">
+      <c r="W25" s="13" t="n">
         <v>4.9</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="Y25" s="3" t="n">
         <v>67.2</v>
@@ -2615,23 +2606,23 @@
       <c r="C26" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="D26" s="9" t="n">
+      <c r="D26" s="8" t="n">
         <v>28.6</v>
       </c>
-      <c r="E26" s="9" t="n">
+      <c r="E26" s="8" t="n">
         <v>19.2</v>
       </c>
-      <c r="F26" s="9" t="n">
+      <c r="F26" s="8" t="n">
         <v>23.9</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>28.4</v>
+        <v>18.4</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>16.7</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>1.9</v>
@@ -2639,17 +2630,17 @@
       <c r="K26" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="L26" s="9" t="n">
+      <c r="L26" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>29.9</v>
+        <v>29.6</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>9.1</v>
+        <v>91.2</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>0</v>
@@ -2658,7 +2649,7 @@
         <v>25.8</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>23.3</v>
+        <v>29.3</v>
       </c>
       <c r="S26" s="3" t="n">
         <v>27.1</v>
@@ -2698,16 +2689,16 @@
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr"/>
-      <c r="D27" s="9" t="n">
+      <c r="D27" s="8" t="n">
         <v>27.3</v>
       </c>
-      <c r="E27" s="9" t="n">
+      <c r="E27" s="8" t="n">
         <v>17.4</v>
       </c>
-      <c r="F27" s="9" t="n">
+      <c r="F27" s="8" t="n">
         <v>22.4</v>
       </c>
-      <c r="G27" s="9" t="n">
+      <c r="G27" s="8" t="n">
         <v>9.9</v>
       </c>
       <c r="H27" s="3" t="n">
@@ -2720,16 +2711,16 @@
         <v>3</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="L27" s="9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="L27" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="M27" s="14" t="n">
-        <v>1.8</v>
+      <c r="M27" s="3" t="n">
+        <v>18</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>19.1</v>
+        <v>18.2</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>98.2</v>
@@ -2747,7 +2738,7 @@
         <v>23.9</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>2.5</v>
+        <v>0.1</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>10.9</v>
@@ -2781,16 +2772,16 @@
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr"/>
-      <c r="D28" s="9" t="n">
+      <c r="D28" s="8" t="n">
         <v>32.7</v>
       </c>
-      <c r="E28" s="9" t="n">
+      <c r="E28" s="8" t="n">
         <v>15.9</v>
       </c>
-      <c r="F28" s="9" t="n">
+      <c r="F28" s="8" t="n">
         <v>24.3</v>
       </c>
-      <c r="G28" s="9" t="n">
+      <c r="G28" s="8" t="n">
         <v>16.8</v>
       </c>
       <c r="H28" s="3" t="n">
@@ -2805,23 +2796,23 @@
       <c r="K28" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="L28" s="9" t="n">
+      <c r="L28" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>16.8</v>
+        <v>16.2</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>1.8</v>
+        <v>18.8</v>
       </c>
       <c r="O28" s="3" t="n">
         <v>92.8</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>20.1</v>
+        <v>30.1</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>23.3</v>
@@ -2833,16 +2824,16 @@
         <v>40.2</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>18.2</v>
+        <v>12.2</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>21</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>21.1</v>
+        <v>27.8</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>20.2</v>
+        <v>216.2</v>
       </c>
       <c r="Y28" s="3" t="n">
         <v>14.6</v>
@@ -2864,13 +2855,13 @@
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr"/>
-      <c r="D29" s="9" t="n">
+      <c r="D29" s="8" t="n">
         <v>30.1</v>
       </c>
-      <c r="E29" s="9" t="n">
+      <c r="E29" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="F29" s="9" t="n">
+      <c r="F29" s="8" t="n">
         <v>24.3</v>
       </c>
       <c r="G29" s="3" t="n">
@@ -2888,10 +2879,10 @@
       <c r="K29" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="L29" s="9" t="n">
+      <c r="L29" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="M29" s="13" t="inlineStr"/>
+      <c r="M29" s="12" t="inlineStr"/>
       <c r="N29" s="3" t="n">
         <v>9.6</v>
       </c>
@@ -2908,7 +2899,7 @@
         <v>21.2</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>24.5</v>
+        <v>14.5</v>
       </c>
       <c r="T29" s="3" t="n">
         <v>72.2</v>
@@ -2929,7 +2920,7 @@
         <v>2.3</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2945,16 +2936,16 @@
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr"/>
-      <c r="D30" s="9" t="n">
+      <c r="D30" s="8" t="n">
         <v>148.4</v>
       </c>
-      <c r="E30" s="9" t="n">
+      <c r="E30" s="8" t="n">
         <v>89.59999999999999</v>
       </c>
-      <c r="F30" s="9" t="n">
-        <v>119</v>
-      </c>
-      <c r="G30" s="9" t="n">
+      <c r="F30" s="8" t="n">
+        <v>119.1</v>
+      </c>
+      <c r="G30" s="8" t="n">
         <v>58.8</v>
       </c>
       <c r="H30" s="3" t="n">
@@ -2966,41 +2957,41 @@
       <c r="J30" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="K30" s="15" t="n">
+      <c r="K30" s="14" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="L30" s="9" t="n">
-        <v>91.7</v>
-      </c>
-      <c r="M30" s="15" t="n">
-        <v>9.199999999999999</v>
+      <c r="L30" s="14" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="M30" s="14" t="n">
+        <v>92.09999999999999</v>
       </c>
       <c r="N30" s="3" t="inlineStr"/>
       <c r="O30" s="3" t="n">
-        <v>45.7</v>
+        <v>45.1</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" s="15" t="n">
+      <c r="Q30" s="14" t="n">
         <v>130.7</v>
       </c>
-      <c r="R30" s="15" t="n">
-        <v>12.9</v>
+      <c r="R30" s="14" t="n">
+        <v>112.9</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>126.4</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>222.2</v>
+        <v>322.2</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="V30" s="15" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="W30" s="15" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="V30" s="14" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="W30" s="14" t="n">
         <v>114.6</v>
       </c>
       <c r="X30" s="3" t="n">
@@ -3026,14 +3017,14 @@
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr"/>
-      <c r="D31" s="9" t="n">
+      <c r="D31" s="8" t="n">
         <v>29.7</v>
       </c>
-      <c r="E31" s="9" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="F31" s="9" t="n">
-        <v>23.9</v>
+      <c r="E31" s="8" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="F31" s="8" t="n">
+        <v>23.8</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>19.8</v>
@@ -3048,25 +3039,25 @@
         <v>2.6</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="9" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="M31" s="9" t="n">
+      <c r="L31" s="14" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="M31" s="14" t="n">
         <v>18.5</v>
       </c>
-      <c r="N31" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="O31" s="9" t="n">
-        <v>100</v>
-      </c>
-      <c r="P31" s="9" t="n">
+      <c r="N31" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="P31" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" s="15" t="n">
+      <c r="Q31" s="14" t="n">
         <v>26.1</v>
       </c>
-      <c r="R31" s="15" t="n">
+      <c r="R31" s="14" t="n">
         <v>22.6</v>
       </c>
       <c r="S31" s="3" t="n">
@@ -3078,10 +3069,10 @@
       <c r="U31" s="3" t="n">
         <v>8.9</v>
       </c>
-      <c r="V31" s="15" t="n">
+      <c r="V31" s="14" t="n">
         <v>20.8</v>
       </c>
-      <c r="W31" s="15" t="n">
+      <c r="W31" s="14" t="n">
         <v>22.9</v>
       </c>
       <c r="X31" s="3" t="n">
@@ -3109,73 +3100,71 @@
       <c r="C32" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="D32" s="3" t="n">
-        <v>38.8</v>
-      </c>
-      <c r="E32" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F32" s="14" t="n">
-        <v>35</v>
+      <c r="D32" s="8" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="F32" s="8" t="n">
+        <v>25.6</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>14.5</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>9.4</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="K32" s="9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K32" s="8" t="n">
         <v>22.5</v>
       </c>
-      <c r="L32" s="13" t="inlineStr"/>
+      <c r="L32" s="12" t="inlineStr"/>
       <c r="M32" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>91.59999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="P32" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q32" s="9" t="n">
+      <c r="Q32" s="8" t="n">
         <v>29.9</v>
       </c>
-      <c r="R32" s="3" t="n">
+      <c r="R32" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="S32" s="3" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="T32" s="3" t="n">
-        <v>35.8</v>
-      </c>
-      <c r="U32" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="V32" s="9" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="W32" s="9" t="n">
+      <c r="S32" s="8" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="V32" s="8" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="W32" s="8" t="n">
         <v>25.8</v>
       </c>
-      <c r="X32" s="9" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="Y32" s="9" t="n">
-        <v>124.2</v>
-      </c>
-      <c r="Z32" s="9" t="n">
-        <v>-6.5</v>
-      </c>
+      <c r="X32" s="3" t="n">
+        <v>85.3</v>
+      </c>
+      <c r="Y32" s="3" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="Z32" s="3" t="inlineStr"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -3192,13 +3181,13 @@
       <c r="C33" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D33" s="9" t="n">
+      <c r="D33" s="8" t="n">
         <v>32.6</v>
       </c>
-      <c r="E33" s="9" t="n">
+      <c r="E33" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="F33" s="9" t="n">
+      <c r="F33" s="8" t="n">
         <v>25.3</v>
       </c>
       <c r="G33" s="3" t="n">
@@ -3213,51 +3202,51 @@
       <c r="J33" s="3" t="n">
         <v>4.5</v>
       </c>
-      <c r="K33" s="9" t="n">
+      <c r="K33" s="8" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="M33" s="14" t="n">
+      <c r="M33" s="13" t="n">
         <v>1.8</v>
       </c>
       <c r="N33" s="3" t="inlineStr"/>
       <c r="O33" s="3" t="n">
-        <v>9</v>
+        <v>90.3</v>
       </c>
       <c r="P33" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" s="9" t="n">
+      <c r="Q33" s="8" t="n">
         <v>28.9</v>
       </c>
-      <c r="R33" s="3" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="S33" s="3" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="T33" s="3" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="U33" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="V33" s="9" t="n">
+      <c r="R33" s="8" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="S33" s="8" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="V33" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="W33" s="9" t="n">
+      <c r="W33" s="8" t="n">
         <v>27.4</v>
       </c>
-      <c r="X33" s="9" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="Y33" s="9" t="n">
-        <v>138.1</v>
-      </c>
-      <c r="Z33" s="9" t="n">
-        <v>-10.1</v>
+      <c r="X33" s="3" t="n">
+        <v>80.3</v>
+      </c>
+      <c r="Y33" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Z33" s="3" t="n">
+        <v>15</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3273,18 +3262,18 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D34" s="9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D34" s="8" t="n">
         <v>32.2</v>
       </c>
-      <c r="E34" s="9" t="n">
+      <c r="E34" s="8" t="n">
         <v>19.5</v>
       </c>
-      <c r="F34" s="9" t="n">
+      <c r="F34" s="8" t="n">
         <v>25.8</v>
       </c>
-      <c r="G34" s="9" t="n">
+      <c r="G34" s="8" t="n">
         <v>12.7</v>
       </c>
       <c r="H34" s="3" t="n">
@@ -3296,17 +3285,17 @@
       <c r="J34" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K34" s="9" t="n">
+      <c r="K34" s="8" t="n">
         <v>13.5</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="M34" s="14" t="n">
+      <c r="M34" s="13" t="n">
         <v>1.9</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>87.2</v>
@@ -3314,35 +3303,35 @@
       <c r="P34" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q34" s="9" t="n">
+      <c r="Q34" s="8" t="n">
         <v>24.8</v>
       </c>
-      <c r="R34" s="3" t="n">
+      <c r="R34" s="8" t="n">
         <v>20.9</v>
       </c>
-      <c r="S34" s="3" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="T34" s="3" t="n">
-        <v>67.2</v>
-      </c>
-      <c r="U34" s="3" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="V34" s="9" t="n">
+      <c r="S34" s="8" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="V34" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="W34" s="9" t="n">
+      <c r="W34" s="8" t="n">
         <v>21.5</v>
       </c>
-      <c r="X34" s="9" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="Y34" s="9" t="n">
-        <v>109.7</v>
-      </c>
-      <c r="Z34" s="9" t="n">
-        <v>-2.3</v>
+      <c r="X34" s="3" t="n">
+        <v>86.3</v>
+      </c>
+      <c r="Y34" s="3" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="Z34" s="3" t="n">
+        <v>9</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3360,16 +3349,16 @@
       <c r="C35" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="D35" s="9" t="n">
+      <c r="D35" s="8" t="n">
         <v>30.4</v>
       </c>
-      <c r="E35" s="9" t="n">
+      <c r="E35" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="F35" s="9" t="n">
+      <c r="F35" s="8" t="n">
         <v>24.4</v>
       </c>
-      <c r="G35" s="9" t="n">
+      <c r="G35" s="8" t="n">
         <v>12</v>
       </c>
       <c r="H35" s="3" t="n">
@@ -3381,17 +3370,17 @@
       <c r="J35" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="K35" s="9" t="n">
+      <c r="K35" s="8" t="n">
         <v>1.6</v>
       </c>
       <c r="L35" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="M35" s="14" t="n">
-        <v>1.8</v>
+      <c r="M35" s="13" t="n">
+        <v>1.9</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>0.1</v>
+        <v>28.6</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>92.2</v>
@@ -3399,35 +3388,35 @@
       <c r="P35" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="Q35" s="9" t="n">
+      <c r="Q35" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="R35" s="3" t="n">
+      <c r="R35" s="8" t="n">
         <v>22.8</v>
       </c>
-      <c r="S35" s="3" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="T35" s="3" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="U35" s="3" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="V35" s="9" t="n">
+      <c r="S35" s="8" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="V35" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="W35" s="9" t="n">
+      <c r="W35" s="8" t="n">
         <v>24.2</v>
       </c>
-      <c r="X35" s="9" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="Y35" s="9" t="n">
-        <v>114.2</v>
-      </c>
-      <c r="Z35" s="9" t="n">
-        <v>-3.8</v>
+      <c r="X35" s="3" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="Y35" s="3" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="Z35" s="3" t="n">
+        <v>53.2</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3443,17 +3432,17 @@
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr"/>
-      <c r="D36" s="14" t="n">
-        <v>93.59999999999999</v>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="F36" s="3" t="n">
+      <c r="D36" s="8" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="E36" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="F36" s="8" t="n">
         <v>25.8</v>
       </c>
-      <c r="G36" s="3" t="n">
-        <v>1.5</v>
+      <c r="G36" s="8" t="n">
+        <v>15.6</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>15.4</v>
@@ -3464,17 +3453,17 @@
       <c r="J36" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="K36" s="9" t="n">
+      <c r="K36" s="8" t="n">
         <v>11.5</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="M36" s="14" t="n">
-        <v>1.8</v>
+      <c r="M36" s="13" t="n">
+        <v>1.2</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>2.5</v>
+        <v>8.6</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>90.2</v>
@@ -3482,35 +3471,35 @@
       <c r="P36" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="Q36" s="9" t="n">
+      <c r="Q36" s="8" t="n">
         <v>31.2</v>
       </c>
-      <c r="R36" s="3" t="n">
+      <c r="R36" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="S36" s="3" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="T36" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="U36" s="3" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="V36" s="9" t="n">
+      <c r="S36" s="8" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="V36" s="8" t="n">
         <v>23.9</v>
       </c>
-      <c r="W36" s="9" t="n">
+      <c r="W36" s="8" t="n">
         <v>27</v>
       </c>
-      <c r="X36" s="9" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="Y36" s="9" t="n">
-        <v>120.3</v>
-      </c>
-      <c r="Z36" s="9" t="n">
-        <v>-6</v>
+      <c r="X36" s="3" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="Y36" s="3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z36" s="3" t="n">
+        <v>17.6</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3526,13 +3515,13 @@
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr"/>
-      <c r="D37" s="9" t="n">
+      <c r="D37" s="8" t="n">
         <v>161.5</v>
       </c>
-      <c r="E37" s="15" t="n">
-        <v>92.5</v>
-      </c>
-      <c r="F37" s="9" t="n">
+      <c r="E37" s="8" t="n">
+        <v>92</v>
+      </c>
+      <c r="F37" s="8" t="n">
         <v>126.9</v>
       </c>
       <c r="G37" s="3" t="n">
@@ -3547,32 +3536,32 @@
       <c r="J37" s="3" t="n">
         <v>20.3</v>
       </c>
-      <c r="K37" s="9" t="n">
+      <c r="K37" s="8" t="n">
         <v>49.1</v>
       </c>
-      <c r="L37" s="15" t="n">
+      <c r="L37" s="14" t="n">
         <v>95.09999999999999</v>
       </c>
-      <c r="M37" s="15" t="n">
-        <v>2.1</v>
+      <c r="M37" s="14" t="n">
+        <v>9.199999999999999</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>50.2</v>
+        <v>150.4</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q37" s="9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Q37" s="8" t="n">
         <v>142.8</v>
       </c>
-      <c r="R37" s="15" t="n">
-        <v>17.5</v>
+      <c r="R37" s="8" t="n">
+        <v>117.5</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>120.4</v>
+        <v>190.4</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>70.3</v>
@@ -3580,10 +3569,10 @@
       <c r="U37" s="3" t="n">
         <v>124.7</v>
       </c>
-      <c r="V37" s="9" t="n">
-        <v>110.1</v>
-      </c>
-      <c r="W37" s="9" t="n">
+      <c r="V37" s="8" t="n">
+        <v>110</v>
+      </c>
+      <c r="W37" s="8" t="n">
         <v>125.9</v>
       </c>
       <c r="X37" s="3" t="n">
@@ -3593,7 +3582,7 @@
         <v>37.2</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>24.7</v>
+        <v>247.2</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3609,16 +3598,16 @@
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr"/>
-      <c r="D38" s="14" t="n">
-        <v>92.3</v>
-      </c>
-      <c r="E38" s="15" t="n">
+      <c r="D38" s="8" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="E38" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="F38" s="15" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="G38" s="3" t="n">
+      <c r="F38" s="8" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="G38" s="8" t="n">
         <v>13.9</v>
       </c>
       <c r="H38" s="3" t="n">
@@ -3631,16 +3620,16 @@
         <v>4.1</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>555.5</v>
-      </c>
-      <c r="L38" s="15" t="n">
-        <v>12</v>
-      </c>
-      <c r="M38" s="15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L38" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="M38" s="14" t="n">
         <v>7.8</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>1.5</v>
+        <v>18.6</v>
       </c>
       <c r="O38" s="3" t="n">
         <v>90.90000000000001</v>
@@ -3648,35 +3637,35 @@
       <c r="P38" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="Q38" s="9" t="n">
+      <c r="Q38" s="8" t="n">
         <v>28.6</v>
       </c>
-      <c r="R38" s="15" t="n">
+      <c r="R38" s="8" t="n">
         <v>23.5</v>
       </c>
-      <c r="S38" s="3" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="T38" s="3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="U38" s="3" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="V38" s="9" t="n">
+      <c r="S38" s="8" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="V38" s="8" t="n">
         <v>22.2</v>
       </c>
-      <c r="W38" s="9" t="n">
+      <c r="W38" s="8" t="n">
         <v>25.2</v>
       </c>
-      <c r="X38" s="9" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="Y38" s="9" t="n">
-        <v>119.8</v>
-      </c>
-      <c r="Z38" s="9" t="n">
-        <v>-5.3</v>
+      <c r="X38" s="3" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="Y38" s="3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Z38" s="3" t="n">
+        <v>14.1</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3695,7 +3684,7 @@
       <c r="D39" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="E39" s="14" t="n">
+      <c r="E39" s="13" t="n">
         <v>45.3</v>
       </c>
       <c r="F39" s="3" t="n">
@@ -3713,18 +3702,18 @@
       <c r="J39" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="K39" s="9" t="n">
+      <c r="K39" s="8" t="n">
         <v>6.2</v>
       </c>
       <c r="L39" s="3" t="n">
         <v>19</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N39" s="3" t="inlineStr"/>
       <c r="O39" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>0</v>
@@ -3736,7 +3725,7 @@
         <v>22.6</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>23.1</v>
+        <v>25.1</v>
       </c>
       <c r="T39" s="3" t="n">
         <v>61.2</v>
@@ -3747,14 +3736,14 @@
       <c r="V39" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="W39" s="14" t="n">
-        <v>24.17</v>
+      <c r="W39" s="13" t="n">
+        <v>24.1</v>
       </c>
       <c r="X39" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Z39" s="3" t="n">
         <v>22</v>
@@ -3775,16 +3764,16 @@
       <c r="C40" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="D40" s="9" t="n">
+      <c r="D40" s="8" t="n">
         <v>32.5</v>
       </c>
-      <c r="E40" s="9" t="n">
+      <c r="E40" s="8" t="n">
         <v>18.3</v>
       </c>
-      <c r="F40" s="9" t="n">
+      <c r="F40" s="8" t="n">
         <v>25.4</v>
       </c>
-      <c r="G40" s="9" t="n">
+      <c r="G40" s="8" t="n">
         <v>14.2</v>
       </c>
       <c r="H40" s="3" t="n">
@@ -3796,17 +3785,17 @@
       <c r="J40" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="K40" s="9" t="n">
+      <c r="K40" s="8" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>18.8</v>
+        <v>18.2</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>1.1</v>
+        <v>29.8</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>92.2</v>
@@ -3815,7 +3804,7 @@
         <v>0.2</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>21.2</v>
+        <v>31.2</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>28.2</v>
@@ -3827,22 +3816,22 @@
         <v>47.2</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="V40" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>25.1</v>
+        <v>25.8</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>20.6</v>
+        <v>21.6</v>
       </c>
       <c r="Y40" s="3" t="n">
         <v>2.6</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>2.5</v>
+        <v>26.9</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3858,17 +3847,17 @@
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr"/>
-      <c r="D41" s="9" t="n">
+      <c r="D41" s="8" t="n">
         <v>31.8</v>
       </c>
-      <c r="E41" s="9" t="n">
+      <c r="E41" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="F41" s="9" t="n">
+      <c r="F41" s="8" t="n">
         <v>25.4</v>
       </c>
-      <c r="G41" s="9" t="n">
-        <v>12.8</v>
+      <c r="G41" s="3" t="n">
+        <v>82.8</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>17</v>
@@ -3879,7 +3868,7 @@
       <c r="J41" s="3" t="n">
         <v>4.1</v>
       </c>
-      <c r="K41" s="9" t="n">
+      <c r="K41" s="8" t="n">
         <v>0</v>
       </c>
       <c r="L41" s="3" t="n">
@@ -3917,7 +3906,7 @@
         <v>24.2</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>2.6</v>
@@ -3939,7 +3928,7 @@
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr"/>
-      <c r="D42" s="13" t="inlineStr"/>
+      <c r="D42" s="12" t="inlineStr"/>
       <c r="E42" s="3" t="n">
         <v>18.8</v>
       </c>
@@ -3950,7 +3939,7 @@
         <v>25.6</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>2</v>
@@ -3958,7 +3947,7 @@
       <c r="J42" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="K42" s="9" t="n">
+      <c r="K42" s="8" t="n">
         <v>1.5</v>
       </c>
       <c r="L42" s="3" t="n">
@@ -3968,7 +3957,7 @@
         <v>19.3</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>0.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O42" s="3" t="n">
         <v>92.2</v>
@@ -3986,16 +3975,16 @@
         <v>24.6</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="V42" s="14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W42" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>3.6</v>
+      </c>
+      <c r="V42" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W42" s="13" t="n">
+        <v>0.2</v>
       </c>
       <c r="X42" s="3" t="inlineStr"/>
       <c r="Y42" s="3" t="inlineStr"/>
@@ -4016,26 +4005,26 @@
       <c r="C43" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D43" s="13" t="inlineStr"/>
-      <c r="E43" s="13" t="inlineStr"/>
-      <c r="F43" s="13" t="inlineStr"/>
+      <c r="D43" s="12" t="inlineStr"/>
+      <c r="E43" s="12" t="inlineStr"/>
+      <c r="F43" s="12" t="inlineStr"/>
       <c r="G43" s="3" t="inlineStr"/>
       <c r="H43" s="3" t="inlineStr"/>
       <c r="I43" s="3" t="inlineStr"/>
       <c r="J43" s="3" t="inlineStr"/>
-      <c r="K43" s="9" t="inlineStr"/>
-      <c r="L43" s="13" t="inlineStr"/>
-      <c r="M43" s="13" t="inlineStr"/>
+      <c r="K43" s="8" t="inlineStr"/>
+      <c r="L43" s="12" t="inlineStr"/>
+      <c r="M43" s="12" t="inlineStr"/>
       <c r="N43" s="3" t="inlineStr"/>
       <c r="O43" s="3" t="inlineStr"/>
       <c r="P43" s="3" t="inlineStr"/>
-      <c r="Q43" s="13" t="inlineStr"/>
-      <c r="R43" s="13" t="inlineStr"/>
+      <c r="Q43" s="12" t="inlineStr"/>
+      <c r="R43" s="12" t="inlineStr"/>
       <c r="S43" s="3" t="inlineStr"/>
       <c r="T43" s="3" t="inlineStr"/>
       <c r="U43" s="3" t="inlineStr"/>
-      <c r="V43" s="13" t="inlineStr"/>
-      <c r="W43" s="13" t="inlineStr"/>
+      <c r="V43" s="12" t="inlineStr"/>
+      <c r="W43" s="12" t="inlineStr"/>
       <c r="X43" s="3" t="inlineStr"/>
       <c r="Y43" s="3" t="inlineStr"/>
       <c r="Z43" s="3" t="inlineStr"/>
@@ -4055,26 +4044,26 @@
       <c r="C44" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D44" s="13" t="inlineStr"/>
-      <c r="E44" s="13" t="inlineStr"/>
-      <c r="F44" s="13" t="inlineStr"/>
+      <c r="D44" s="12" t="inlineStr"/>
+      <c r="E44" s="12" t="inlineStr"/>
+      <c r="F44" s="12" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr"/>
-      <c r="K44" s="9" t="inlineStr"/>
-      <c r="L44" s="13" t="inlineStr"/>
-      <c r="M44" s="13" t="inlineStr"/>
+      <c r="K44" s="8" t="inlineStr"/>
+      <c r="L44" s="12" t="inlineStr"/>
+      <c r="M44" s="12" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="13" t="inlineStr"/>
-      <c r="R44" s="13" t="inlineStr"/>
+      <c r="Q44" s="12" t="inlineStr"/>
+      <c r="R44" s="12" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
       <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="13" t="inlineStr"/>
-      <c r="W44" s="13" t="inlineStr"/>
+      <c r="V44" s="12" t="inlineStr"/>
+      <c r="W44" s="12" t="inlineStr"/>
       <c r="X44" s="3" t="inlineStr"/>
       <c r="Y44" s="3" t="inlineStr"/>
       <c r="Z44" s="3" t="inlineStr"/>
@@ -4092,16 +4081,16 @@
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr"/>
-      <c r="D45" s="9" t="n">
-        <v>129.4</v>
-      </c>
-      <c r="E45" s="9" t="n">
-        <v>74.59999999999999</v>
-      </c>
-      <c r="F45" s="9" t="n">
+      <c r="D45" s="14" t="n">
+        <v>122.3</v>
+      </c>
+      <c r="E45" s="14" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="F45" s="14" t="n">
         <v>102</v>
       </c>
-      <c r="G45" s="9" t="n">
+      <c r="G45" s="3" t="n">
         <v>54.7</v>
       </c>
       <c r="H45" s="3" t="n">
@@ -4113,14 +4102,14 @@
       <c r="J45" s="3" t="n">
         <v>15.6</v>
       </c>
-      <c r="K45" s="9" t="n">
+      <c r="K45" s="8" t="n">
         <v>7.7</v>
       </c>
-      <c r="L45" s="15" t="n">
-        <v>74.59999999999999</v>
-      </c>
-      <c r="M45" s="15" t="n">
-        <v>11.2</v>
+      <c r="L45" s="14" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="M45" s="14" t="n">
+        <v>11.1</v>
       </c>
       <c r="N45" s="3" t="inlineStr"/>
       <c r="O45" s="3" t="n">
@@ -4129,35 +4118,35 @@
       <c r="P45" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q45" s="15" t="n">
-        <v>106.7</v>
-      </c>
-      <c r="R45" s="15" t="n">
+      <c r="Q45" s="14" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="R45" s="14" t="n">
         <v>102.7</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>241.8</v>
+        <v>241.2</v>
       </c>
       <c r="T45" s="3" t="n">
         <v>38.7</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>95.3</v>
-      </c>
-      <c r="V45" s="15" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="V45" s="14" t="n">
         <v>85.7</v>
       </c>
-      <c r="W45" s="15" t="n">
+      <c r="W45" s="14" t="n">
         <v>96.3</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>232.7</v>
+        <v>327.2</v>
       </c>
       <c r="Y45" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4173,13 +4162,13 @@
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr"/>
-      <c r="D46" s="14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E46" s="15" t="n">
+      <c r="D46" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E46" s="14" t="n">
         <v>32.3</v>
       </c>
-      <c r="F46" s="15" t="n">
+      <c r="F46" s="14" t="n">
         <v>18.7</v>
       </c>
       <c r="G46" s="3" t="n">
@@ -4195,27 +4184,27 @@
         <v>13.7</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L46" s="15" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="M46" s="15" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="L46" s="14" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="M46" s="14" t="n">
         <v>19.9</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>2.2</v>
+        <v>22.3</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>26.7</v>
       </c>
-      <c r="Q46" s="15" t="n">
+      <c r="Q46" s="14" t="n">
         <v>0.2</v>
       </c>
-      <c r="R46" s="15" t="n">
+      <c r="R46" s="14" t="n">
         <v>25.7</v>
       </c>
       <c r="S46" s="3" t="n">
@@ -4225,20 +4214,22 @@
         <v>9.199999999999999</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="V46" s="15" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="V46" s="14" t="n">
         <v>21.4</v>
       </c>
-      <c r="W46" s="15" t="n">
+      <c r="W46" s="14" t="n">
         <v>24.1</v>
       </c>
       <c r="X46" s="3" t="n">
         <v>60.2</v>
       </c>
-      <c r="Y46" s="3" t="inlineStr"/>
+      <c r="Y46" s="3" t="n">
+        <v>2.1</v>
+      </c>
       <c r="Z46" s="3" t="n">
-        <v>2.2</v>
+        <v>298.9</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_recalcmultiday.xlsx
+++ b/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_recalcmultiday.xlsx
@@ -820,17 +820,17 @@
       <c r="Q4" s="8" t="n">
         <v>30.6</v>
       </c>
-      <c r="R4" s="3" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="S4" s="3" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="T4" s="3" t="n">
-        <v>45.2</v>
-      </c>
-      <c r="U4" s="3" t="n">
-        <v>18.6</v>
+      <c r="R4" s="8" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="S4" s="8" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="U4" s="8" t="n">
+        <v>14.5</v>
       </c>
       <c r="V4" s="8" t="n">
         <v>27.5</v>
@@ -903,17 +903,17 @@
       <c r="Q5" s="8" t="n">
         <v>23.9</v>
       </c>
-      <c r="R5" s="3" t="n">
+      <c r="R5" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="S5" s="3" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="T5" s="3" t="n">
-        <v>70.2</v>
-      </c>
-      <c r="U5" s="3" t="n">
-        <v>6.5</v>
+      <c r="S5" s="8" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v>4.8</v>
       </c>
       <c r="V5" s="8" t="n">
         <v>23.1</v>
@@ -966,7 +966,7 @@
         <v>4.4</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L6" s="8" t="n">
         <v>17.4</v>
@@ -975,7 +975,7 @@
         <v>17.5</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>12.8</v>
+        <v>19.8</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>91.2</v>
@@ -986,17 +986,17 @@
       <c r="Q6" s="8" t="n">
         <v>29.5</v>
       </c>
-      <c r="R6" s="3" t="n">
+      <c r="R6" s="8" t="n">
         <v>24.1</v>
       </c>
-      <c r="S6" s="3" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="T6" s="3" t="n">
-        <v>50.6</v>
-      </c>
-      <c r="U6" s="3" t="n">
-        <v>14.4</v>
+      <c r="S6" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v>11.2</v>
       </c>
       <c r="V6" s="8" t="n">
         <v>27.2</v>
@@ -1073,10 +1073,10 @@
         <v>19.5</v>
       </c>
       <c r="S7" s="8" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="T7" s="8" t="n">
-        <v>96.2</v>
+        <v>96.3</v>
       </c>
       <c r="U7" s="8" t="n">
         <v>0.9</v>
@@ -1132,7 +1132,7 @@
         <v>2.2</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>1.4</v>
+        <v>10.4</v>
       </c>
       <c r="L8" s="8" t="n">
         <v>18.9</v>
@@ -1152,17 +1152,17 @@
       <c r="Q8" s="8" t="n">
         <v>25.8</v>
       </c>
-      <c r="R8" s="3" t="n">
+      <c r="R8" s="8" t="n">
         <v>22.3</v>
       </c>
-      <c r="S8" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="T8" s="3" t="n">
-        <v>66.2</v>
-      </c>
-      <c r="U8" s="3" t="n">
-        <v>8.4</v>
+      <c r="S8" s="8" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v>81</v>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v>6.3</v>
       </c>
       <c r="V8" s="8" t="n">
         <v>24.6</v>
@@ -1235,8 +1235,8 @@
       <c r="Q9" s="8" t="n">
         <v>129.9</v>
       </c>
-      <c r="R9" s="14" t="n">
-        <v>110.1</v>
+      <c r="R9" s="8" t="n">
+        <v>110.8</v>
       </c>
       <c r="S9" s="3" t="n">
         <v>122.3</v>
@@ -1257,7 +1257,7 @@
         <v>12.6</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>382.6</v>
+        <v>382</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>31.1</v>
@@ -1292,7 +1292,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>3.2</v>
@@ -1318,17 +1318,17 @@
       <c r="Q10" s="8" t="n">
         <v>25.9</v>
       </c>
-      <c r="R10" s="14" t="n">
+      <c r="R10" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="S10" s="3" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="T10" s="3" t="n">
-        <v>64.2</v>
-      </c>
-      <c r="U10" s="3" t="n">
-        <v>9.800000000000001</v>
+      <c r="S10" s="8" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v>7</v>
       </c>
       <c r="V10" s="8" t="n">
         <v>24.8</v>
@@ -1373,15 +1373,15 @@
       </c>
       <c r="H11" s="3" t="inlineStr"/>
       <c r="I11" s="3" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J11" s="3" t="inlineStr"/>
       <c r="K11" s="3" t="inlineStr"/>
       <c r="L11" s="3" t="n">
         <v>8.4</v>
       </c>
-      <c r="M11" s="3" t="n">
-        <v>12.3</v>
+      <c r="M11" s="8" t="n">
+        <v>19.3</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>2.8</v>
@@ -1417,7 +1417,7 @@
         <v>26.8</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>81.2</v>
+        <v>81.8</v>
       </c>
       <c r="Z11" s="3" t="n">
         <v>4.5</v>
@@ -1463,20 +1463,20 @@
       <c r="L12" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="M12" s="3" t="n">
+      <c r="M12" s="8" t="n">
         <v>18.8</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>2.8</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>90.2</v>
+        <v>90.5</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="Q12" s="8" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>22</v>
@@ -1485,10 +1485,10 @@
         <v>25.1</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>67.2</v>
+        <v>6.7</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>22.2</v>
@@ -1500,7 +1500,7 @@
         <v>24.4</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>81.2</v>
+        <v>81.8</v>
       </c>
       <c r="Z12" s="3" t="n">
         <v>83.2</v>
@@ -1544,13 +1544,13 @@
         <v>0</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="M13" s="3" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="M13" s="8" t="n">
         <v>18.9</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>90.2</v>
@@ -1568,7 +1568,7 @@
         <v>22.9</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>74.2</v>
+        <v>7.4</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>3.8</v>
@@ -1583,7 +1583,7 @@
         <v>22.6</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="Z13" s="3" t="n">
         <v>2.5</v>
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>10.1</v>
+        <v>0.1</v>
       </c>
       <c r="D14" s="8" t="n">
         <v>29.9</v>
@@ -1626,12 +1626,12 @@
         <v>2.7</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="L14" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="M14" s="3" t="n">
+      <c r="M14" s="8" t="n">
         <v>18.7</v>
       </c>
       <c r="N14" s="3" t="n">
@@ -1650,7 +1650,7 @@
         <v>23.4</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>26.2</v>
+        <v>26.8</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>58.2</v>
@@ -1714,14 +1714,14 @@
       <c r="L15" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="M15" s="3" t="n">
+      <c r="M15" s="8" t="n">
         <v>18.9</v>
       </c>
       <c r="N15" s="3" t="n">
         <v>2.8</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>91.2</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>0.2</v>
@@ -1733,7 +1733,7 @@
         <v>22.9</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>10.7</v>
+        <v>20.7</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>58.2</v>
@@ -1783,26 +1783,26 @@
         <v>9.800000000000001</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>81.5</v>
+        <v>87.5</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>17.3</v>
+        <v>14.3</v>
       </c>
       <c r="K16" s="11" t="inlineStr"/>
       <c r="L16" s="14" t="n">
         <v>95.3</v>
       </c>
-      <c r="M16" s="14" t="n">
+      <c r="M16" s="8" t="n">
         <v>94.59999999999999</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>1</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>153.2</v>
+        <v>35.3</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>1.4</v>
@@ -1823,7 +1823,7 @@
         <v>41.2</v>
       </c>
       <c r="V16" s="14" t="n">
-        <v>116.7</v>
+        <v>11.4</v>
       </c>
       <c r="W16" s="8" t="n">
         <v>107.7</v>
@@ -1832,7 +1832,7 @@
         <v>124.6</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>408.9</v>
+        <v>708.8</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>15</v>
@@ -1851,7 +1851,7 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D17" s="8" t="n">
         <v>28.1</v>
@@ -1866,7 +1866,7 @@
         <v>9.6</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>12.5</v>
+        <v>17.5</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>1.9</v>
@@ -1878,11 +1878,11 @@
       <c r="L17" s="14" t="n">
         <v>19.1</v>
       </c>
-      <c r="M17" s="14" t="n">
+      <c r="M17" s="8" t="n">
         <v>18.9</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>22.1</v>
+        <v>0.2</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>91.2</v>
@@ -1915,7 +1915,7 @@
         <v>24.9</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>82.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z17" s="3" t="n">
         <v>2</v>
@@ -1935,13 +1935,13 @@
       </c>
       <c r="C18" s="3" t="inlineStr"/>
       <c r="D18" s="8" t="n">
-        <v>25.8</v>
+        <v>24.8</v>
       </c>
       <c r="E18" s="8" t="n">
         <v>13.5</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>19.5</v>
+        <v>19.2</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>12.4</v>
@@ -1950,7 +1950,7 @@
         <v>16.6</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>3.6</v>
@@ -1958,10 +1958,10 @@
       <c r="K18" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="8" t="n">
+      <c r="L18" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="M18" s="8" t="n">
+      <c r="M18" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="N18" s="3" t="n">
@@ -1976,7 +1976,7 @@
       <c r="Q18" s="13" t="n">
         <v>89.2</v>
       </c>
-      <c r="R18" s="8" t="n">
+      <c r="R18" s="3" t="n">
         <v>23.2</v>
       </c>
       <c r="S18" s="3" t="n">
@@ -1989,7 +1989,7 @@
         <v>10.1</v>
       </c>
       <c r="V18" s="13" t="n">
-        <v>12.18</v>
+        <v>1.8</v>
       </c>
       <c r="W18" s="3" t="n">
         <v>20.8</v>
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D19" s="8" t="n">
         <v>30.6</v>
@@ -2043,34 +2043,34 @@
       <c r="K19" s="8" t="n">
         <v>27.9</v>
       </c>
-      <c r="L19" s="8" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="M19" s="8" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="N19" s="8" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="O19" s="8" t="n">
-        <v>99.40000000000001</v>
-      </c>
-      <c r="P19" s="8" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="Q19" s="8" t="n">
+      <c r="L19" s="3" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q19" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="R19" s="8" t="n">
+      <c r="R19" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="S19" s="8" t="n">
+      <c r="S19" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="T19" s="8" t="n">
-        <v>99</v>
-      </c>
-      <c r="U19" s="8" t="n">
+      <c r="T19" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="U19" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="V19" s="3" t="n">
@@ -2083,7 +2083,7 @@
         <v>23</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>81.2</v>
+        <v>87.8</v>
       </c>
       <c r="Z19" s="3" t="n">
         <v>0.6</v>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D20" s="8" t="n">
         <v>28.5</v>
@@ -2113,8 +2113,8 @@
       <c r="F20" s="8" t="n">
         <v>23.7</v>
       </c>
-      <c r="G20" s="3" t="n">
-        <v>29.6</v>
+      <c r="G20" s="8" t="n">
+        <v>9.6</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>17.6</v>
@@ -2123,30 +2123,28 @@
         <v>1.2</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="K20" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L20" s="8" t="n">
+      <c r="L20" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="M20" s="8" t="n">
+      <c r="M20" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="N20" s="8" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="O20" s="8" t="n">
-        <v>100</v>
-      </c>
-      <c r="P20" s="8" t="n">
+      <c r="N20" s="3" t="inlineStr"/>
+      <c r="O20" s="3" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="P20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q20" s="3" t="n">
         <v>26.2</v>
       </c>
-      <c r="R20" s="8" t="n">
+      <c r="R20" s="3" t="n">
         <v>21.9</v>
       </c>
       <c r="S20" s="3" t="n">
@@ -2165,7 +2163,7 @@
         <v>20.2</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>25.3</v>
+        <v>85.3</v>
       </c>
       <c r="Y20" s="3" t="n">
         <v>2.6</v>
@@ -2187,7 +2185,7 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="D21" s="8" t="n">
         <v>28.4</v>
@@ -2205,7 +2203,7 @@
         <v>17.3</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" s="3" t="n">
         <v>1.9</v>
@@ -2213,34 +2211,34 @@
       <c r="K21" s="8" t="n">
         <v>3.8</v>
       </c>
-      <c r="L21" s="8" t="n">
+      <c r="L21" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="M21" s="8" t="n">
+      <c r="M21" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="N21" s="8" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="O21" s="8" t="n">
-        <v>93.90000000000001</v>
-      </c>
-      <c r="P21" s="8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q21" s="8" t="n">
+      <c r="N21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="R21" s="8" t="n">
+      <c r="R21" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="S21" s="8" t="n">
+      <c r="S21" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="T21" s="8" t="n">
-        <v>98.90000000000001</v>
-      </c>
-      <c r="U21" s="8" t="n">
+      <c r="T21" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="U21" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="V21" s="3" t="n">
@@ -2250,10 +2248,10 @@
         <v>19.1</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>21.9</v>
+        <v>2.9</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>90.2</v>
+        <v>9</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>0.8</v>
@@ -2272,18 +2270,18 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>29.2</v>
+        <v>30.2</v>
       </c>
       <c r="E22" s="8" t="n">
         <v>17</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="G22" s="8" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="G22" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="H22" s="3" t="n">
@@ -2298,25 +2296,25 @@
       <c r="K22" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="8" t="n">
+      <c r="L22" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="M22" s="8" t="n">
+      <c r="M22" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="N22" s="8" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="O22" s="8" t="n">
-        <v>100</v>
-      </c>
-      <c r="P22" s="8" t="n">
+      <c r="N22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="P22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q22" s="3" t="n">
         <v>28.5</v>
       </c>
-      <c r="R22" s="8" t="n">
+      <c r="R22" s="3" t="n">
         <v>23.1</v>
       </c>
       <c r="S22" s="3" t="n">
@@ -2326,7 +2324,7 @@
         <v>56.2</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>19.9</v>
+        <v>13.9</v>
       </c>
       <c r="V22" s="3" t="n">
         <v>24.6</v>
@@ -2335,7 +2333,7 @@
         <v>26.2</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>22.6</v>
+        <v>28.6</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>80.2</v>
@@ -2381,33 +2379,33 @@
       <c r="K23" s="8" t="n">
         <v>31.7</v>
       </c>
-      <c r="L23" s="8" t="n">
-        <v>94.09999999999999</v>
-      </c>
-      <c r="M23" s="8" t="n">
-        <v>93.40000000000001</v>
+      <c r="L23" s="14" t="n">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="M23" s="14" t="n">
+        <v>92.90000000000001</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>451.2</v>
+        <v>45.7</v>
       </c>
       <c r="P23" s="3" t="inlineStr"/>
       <c r="Q23" s="14" t="n">
         <v>121</v>
       </c>
-      <c r="R23" s="8" t="n">
-        <v>107.2</v>
+      <c r="R23" s="14" t="n">
+        <v>107.8</v>
       </c>
       <c r="S23" s="3" t="n">
         <v>119.7</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>360.2</v>
+        <v>36</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>34.7</v>
+        <v>57.7</v>
       </c>
       <c r="V23" s="14" t="n">
         <v>108.4</v>
@@ -2416,7 +2414,7 @@
         <v>102.6</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>117.8</v>
+        <v>117.7</v>
       </c>
       <c r="Y23" s="3" t="n">
         <v>427.6</v>
@@ -2462,34 +2460,34 @@
         <v>1.8</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L24" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L24" s="14" t="n">
         <v>18.8</v>
       </c>
-      <c r="M24" s="8" t="n">
+      <c r="M24" s="14" t="n">
         <v>18.6</v>
       </c>
-      <c r="N24" s="8" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="O24" s="8" t="n">
-        <v>98.8</v>
-      </c>
-      <c r="P24" s="8" t="n">
-        <v>0.3</v>
+      <c r="N24" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>0.2</v>
       </c>
       <c r="Q24" s="14" t="n">
         <v>27.2</v>
       </c>
-      <c r="R24" s="8" t="n">
-        <v>21.4</v>
+      <c r="R24" s="14" t="n">
+        <v>2</v>
       </c>
       <c r="S24" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>72.2</v>
+        <v>78.8</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>6.9</v>
@@ -2507,7 +2505,7 @@
         <v>2.5</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>85.59999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2530,7 +2528,7 @@
         <v>18.7</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="G25" s="13" t="n">
         <v>44.4</v>
@@ -2547,19 +2545,19 @@
       <c r="K25" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L25" s="3" t="n">
+      <c r="L25" s="8" t="n">
         <v>19.1</v>
       </c>
-      <c r="M25" s="3" t="n">
+      <c r="M25" s="8" t="n">
         <v>19.1</v>
       </c>
-      <c r="N25" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="O25" s="3" t="n">
-        <v>92.2</v>
-      </c>
-      <c r="P25" s="3" t="n">
+      <c r="N25" s="8" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="O25" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="P25" s="8" t="n">
         <v>0</v>
       </c>
       <c r="Q25" s="13" t="n">
@@ -2587,7 +2585,7 @@
         <v>23.1</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>67.2</v>
+        <v>67.3</v>
       </c>
       <c r="Z25" s="3" t="inlineStr"/>
       <c r="AA25" s="3" t="inlineStr">
@@ -2604,7 +2602,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="D26" s="8" t="n">
         <v>28.6</v>
@@ -2616,13 +2614,13 @@
         <v>23.9</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>18.4</v>
+        <v>8.4</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>16.7</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>1.9</v>
@@ -2630,17 +2628,17 @@
       <c r="K26" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="L26" s="3" t="n">
+      <c r="L26" s="8" t="n">
         <v>19.6</v>
       </c>
       <c r="M26" s="3" t="n">
         <v>29.6</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>91.2</v>
+        <v>91.8</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>0</v>
@@ -2649,13 +2647,13 @@
         <v>25.8</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>29.3</v>
+        <v>23.3</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>27.1</v>
+        <v>0.8</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>76.2</v>
+        <v>7.6</v>
       </c>
       <c r="U26" s="3" t="n">
         <v>5.9</v>
@@ -2667,7 +2665,7 @@
         <v>21.3</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>86.2</v>
+        <v>86.8</v>
       </c>
       <c r="Y26" s="3" t="n">
         <v>0.8</v>
@@ -2702,7 +2700,7 @@
         <v>9.9</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>15.8</v>
+        <v>18.8</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>1.9</v>
@@ -2711,25 +2709,25 @@
         <v>3</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="L27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="M27" s="3" t="n">
+      <c r="M27" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="N27" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="O27" s="3" t="n">
-        <v>98.2</v>
-      </c>
-      <c r="P27" s="3" t="n">
+      <c r="N27" s="8" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="O27" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="P27" s="8" t="n">
         <v>0</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>20.6</v>
+        <v>26.6</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>22.1</v>
@@ -2738,7 +2736,7 @@
         <v>23.9</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>0.1</v>
+        <v>6.3</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>10.9</v>
@@ -2796,20 +2794,20 @@
       <c r="K28" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="L28" s="3" t="n">
+      <c r="L28" s="8" t="n">
         <v>16.8</v>
       </c>
       <c r="M28" s="3" t="n">
         <v>16.2</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>18.8</v>
+        <v>0</v>
       </c>
       <c r="O28" s="3" t="n">
         <v>92.8</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>30.1</v>
@@ -2827,16 +2825,16 @@
         <v>12.2</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="W28" s="3" t="n">
         <v>27.8</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>216.2</v>
+        <v>21.2</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>14.6</v>
+        <v>17.6</v>
       </c>
       <c r="Z28" s="3" t="n">
         <v>53.2</v>
@@ -2879,12 +2877,12 @@
       <c r="K29" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="L29" s="3" t="n">
+      <c r="L29" s="8" t="n">
         <v>18.2</v>
       </c>
       <c r="M29" s="12" t="inlineStr"/>
       <c r="N29" s="3" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>90.59999999999999</v>
@@ -2914,7 +2912,7 @@
         <v>21.8</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>86.2</v>
+        <v>86.8</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>2.3</v>
@@ -2943,7 +2941,7 @@
         <v>89.59999999999999</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>119.1</v>
+        <v>119</v>
       </c>
       <c r="G30" s="8" t="n">
         <v>58.8</v>
@@ -2960,15 +2958,15 @@
       <c r="K30" s="14" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="L30" s="14" t="n">
-        <v>92.5</v>
+      <c r="L30" s="8" t="n">
+        <v>91.7</v>
       </c>
       <c r="M30" s="14" t="n">
-        <v>92.09999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="N30" s="3" t="inlineStr"/>
       <c r="O30" s="3" t="n">
-        <v>45.1</v>
+        <v>45.7</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>0</v>
@@ -2989,13 +2987,13 @@
         <v>118.2</v>
       </c>
       <c r="V30" s="14" t="n">
-        <v>104.6</v>
+        <v>10.4</v>
       </c>
       <c r="W30" s="14" t="n">
-        <v>114.6</v>
+        <v>117.6</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>372.2</v>
+        <v>382.8</v>
       </c>
       <c r="Y30" s="3" t="n">
         <v>32.4</v>
@@ -3030,7 +3028,7 @@
         <v>19.8</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>16.1</v>
+        <v>18.1</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>2.1</v>
@@ -3039,23 +3037,23 @@
         <v>2.6</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="14" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="M31" s="14" t="n">
+      <c r="L31" s="8" t="n">
         <v>18.5</v>
       </c>
-      <c r="N31" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="O31" s="3" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="P31" s="3" t="n">
+      <c r="M31" s="8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="N31" s="8" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="O31" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="P31" s="8" t="n">
         <v>0</v>
       </c>
       <c r="Q31" s="14" t="n">
-        <v>26.1</v>
+        <v>26.3</v>
       </c>
       <c r="R31" s="14" t="n">
         <v>22.6</v>
@@ -3098,16 +3096,16 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="D32" s="8" t="n">
         <v>32.8</v>
       </c>
-      <c r="E32" s="8" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="F32" s="8" t="n">
-        <v>25.6</v>
+      <c r="E32" s="13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F32" s="13" t="n">
+        <v>35</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>14.5</v>
@@ -3124,12 +3122,12 @@
       <c r="K32" s="8" t="n">
         <v>22.5</v>
       </c>
-      <c r="L32" s="12" t="inlineStr"/>
+      <c r="L32" s="8" t="inlineStr"/>
       <c r="M32" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>87.59999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>91.2</v>
@@ -3140,19 +3138,19 @@
       <c r="Q32" s="8" t="n">
         <v>29.9</v>
       </c>
-      <c r="R32" s="8" t="n">
+      <c r="R32" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="S32" s="8" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v>70.7</v>
-      </c>
-      <c r="U32" s="8" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="V32" s="8" t="n">
+      <c r="S32" s="3" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="T32" s="3" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="U32" s="3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="V32" s="3" t="n">
         <v>22.1</v>
       </c>
       <c r="W32" s="8" t="n">
@@ -3190,8 +3188,8 @@
       <c r="F33" s="8" t="n">
         <v>25.3</v>
       </c>
-      <c r="G33" s="3" t="n">
-        <v>94.59999999999999</v>
+      <c r="G33" s="8" t="n">
+        <v>14.6</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>17.9</v>
@@ -3205,7 +3203,7 @@
       <c r="K33" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L33" s="3" t="n">
+      <c r="L33" s="8" t="n">
         <v>18.8</v>
       </c>
       <c r="M33" s="13" t="n">
@@ -3213,7 +3211,7 @@
       </c>
       <c r="N33" s="3" t="inlineStr"/>
       <c r="O33" s="3" t="n">
-        <v>90.3</v>
+        <v>80.3</v>
       </c>
       <c r="P33" s="3" t="n">
         <v>0</v>
@@ -3221,20 +3219,20 @@
       <c r="Q33" s="8" t="n">
         <v>28.9</v>
       </c>
-      <c r="R33" s="8" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="S33" s="8" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v>78.59999999999999</v>
-      </c>
-      <c r="U33" s="8" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="V33" s="8" t="n">
-        <v>22</v>
+      <c r="R33" s="3" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="S33" s="3" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="T33" s="3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="U33" s="3" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="V33" s="3" t="n">
+        <v>29</v>
       </c>
       <c r="W33" s="8" t="n">
         <v>27.4</v>
@@ -3288,17 +3286,17 @@
       <c r="K34" s="8" t="n">
         <v>13.5</v>
       </c>
-      <c r="L34" s="3" t="n">
+      <c r="L34" s="8" t="n">
         <v>19.7</v>
       </c>
       <c r="M34" s="13" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>87.2</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>1.2</v>
@@ -3306,26 +3304,26 @@
       <c r="Q34" s="8" t="n">
         <v>24.8</v>
       </c>
-      <c r="R34" s="8" t="n">
+      <c r="R34" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="S34" s="8" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v>78.90000000000001</v>
-      </c>
-      <c r="U34" s="8" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="V34" s="8" t="n">
+      <c r="S34" s="3" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="T34" s="3" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="U34" s="3" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="V34" s="3" t="n">
         <v>20</v>
       </c>
       <c r="W34" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>86.3</v>
+        <v>8.6</v>
       </c>
       <c r="Y34" s="3" t="n">
         <v>6.7</v>
@@ -3347,19 +3345,19 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="D35" s="8" t="n">
         <v>30.4</v>
       </c>
       <c r="E35" s="8" t="n">
-        <v>18.4</v>
+        <v>24.4</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="G35" s="8" t="n">
-        <v>12</v>
+        <v>27.4</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>18</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>18.2</v>
@@ -3373,37 +3371,37 @@
       <c r="K35" s="8" t="n">
         <v>1.6</v>
       </c>
-      <c r="L35" s="3" t="n">
+      <c r="L35" s="8" t="n">
         <v>19</v>
       </c>
       <c r="M35" s="13" t="n">
         <v>1.9</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>92.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Q35" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="R35" s="8" t="n">
+      <c r="R35" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="S35" s="8" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v>73.40000000000001</v>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="V35" s="8" t="n">
+      <c r="S35" s="3" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="T35" s="3" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="U35" s="3" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="V35" s="3" t="n">
         <v>22</v>
       </c>
       <c r="W35" s="8" t="n">
@@ -3451,22 +3449,22 @@
         <v>3</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="K36" s="8" t="n">
         <v>11.5</v>
       </c>
-      <c r="L36" s="3" t="n">
+      <c r="L36" s="8" t="n">
         <v>18.7</v>
       </c>
       <c r="M36" s="13" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>90.2</v>
+        <v>9</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>1</v>
@@ -3474,19 +3472,19 @@
       <c r="Q36" s="8" t="n">
         <v>31.2</v>
       </c>
-      <c r="R36" s="8" t="n">
+      <c r="R36" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="S36" s="8" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v>69.7</v>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="V36" s="8" t="n">
+      <c r="S36" s="3" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="T36" s="3" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="U36" s="3" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="V36" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="W36" s="8" t="n">
@@ -3496,7 +3494,7 @@
         <v>55.2</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z36" s="3" t="n">
         <v>17.6</v>
@@ -3518,10 +3516,10 @@
       <c r="D37" s="8" t="n">
         <v>161.5</v>
       </c>
-      <c r="E37" s="8" t="n">
-        <v>92</v>
-      </c>
-      <c r="F37" s="8" t="n">
+      <c r="E37" s="14" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="F37" s="14" t="n">
         <v>126.9</v>
       </c>
       <c r="G37" s="3" t="n">
@@ -3539,17 +3537,17 @@
       <c r="K37" s="8" t="n">
         <v>49.1</v>
       </c>
-      <c r="L37" s="14" t="n">
-        <v>95.09999999999999</v>
+      <c r="L37" s="8" t="n">
+        <v>76.2</v>
       </c>
       <c r="M37" s="14" t="n">
-        <v>9.199999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>150.4</v>
+        <v>450</v>
       </c>
       <c r="P37" s="3" t="n">
         <v>8.6</v>
@@ -3557,11 +3555,11 @@
       <c r="Q37" s="8" t="n">
         <v>142.8</v>
       </c>
-      <c r="R37" s="8" t="n">
+      <c r="R37" s="14" t="n">
         <v>117.5</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>190.4</v>
+        <v>19</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>70.3</v>
@@ -3569,7 +3567,7 @@
       <c r="U37" s="3" t="n">
         <v>124.7</v>
       </c>
-      <c r="V37" s="8" t="n">
+      <c r="V37" s="14" t="n">
         <v>110</v>
       </c>
       <c r="W37" s="8" t="n">
@@ -3582,7 +3580,7 @@
         <v>37.2</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>247.2</v>
+        <v>24.7</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3599,15 +3597,15 @@
       </c>
       <c r="C38" s="3" t="inlineStr"/>
       <c r="D38" s="8" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="E38" s="8" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="E38" s="14" t="n">
         <v>18.4</v>
       </c>
-      <c r="F38" s="8" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="G38" s="8" t="n">
+      <c r="F38" s="14" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="G38" s="3" t="n">
         <v>13.9</v>
       </c>
       <c r="H38" s="3" t="n">
@@ -3620,39 +3618,39 @@
         <v>4.1</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L38" s="14" t="n">
-        <v>18</v>
+        <v>0</v>
+      </c>
+      <c r="L38" s="8" t="n">
+        <v>19</v>
       </c>
       <c r="M38" s="14" t="n">
-        <v>7.8</v>
+        <v>2.8</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>18.6</v>
+        <v>0</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>90.90000000000001</v>
+        <v>9</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>1.2</v>
       </c>
       <c r="Q38" s="8" t="n">
         <v>28.6</v>
       </c>
-      <c r="R38" s="8" t="n">
+      <c r="R38" s="14" t="n">
         <v>23.5</v>
       </c>
-      <c r="S38" s="8" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v>73.90000000000001</v>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="V38" s="8" t="n">
+      <c r="S38" s="3" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="T38" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="U38" s="3" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="V38" s="14" t="n">
         <v>22.2</v>
       </c>
       <c r="W38" s="8" t="n">
@@ -3662,10 +3660,10 @@
         <v>73.2</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>14.1</v>
+        <v>14.8</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3708,17 +3706,17 @@
       <c r="L39" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="M39" s="3" t="n">
+      <c r="M39" s="8" t="n">
         <v>19</v>
       </c>
       <c r="N39" s="3" t="inlineStr"/>
       <c r="O39" s="3" t="n">
-        <v>96.59999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q39" s="3" t="n">
+      <c r="Q39" s="8" t="n">
         <v>26.4</v>
       </c>
       <c r="R39" s="3" t="n">
@@ -3762,7 +3760,7 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="D40" s="8" t="n">
         <v>32.5</v>
@@ -3791,19 +3789,19 @@
       <c r="L40" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="M40" s="3" t="n">
-        <v>18.2</v>
+      <c r="M40" s="8" t="n">
+        <v>18.8</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>29.8</v>
+        <v>2</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>92.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="P40" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q40" s="3" t="n">
+      <c r="Q40" s="8" t="n">
         <v>31.2</v>
       </c>
       <c r="R40" s="3" t="n">
@@ -3816,7 +3814,7 @@
         <v>47.2</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>19.6</v>
+        <v>19.4</v>
       </c>
       <c r="V40" s="3" t="n">
         <v>22.8</v>
@@ -3825,13 +3823,13 @@
         <v>25.8</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>21.6</v>
+        <v>28.6</v>
       </c>
       <c r="Y40" s="3" t="n">
         <v>2.6</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>26.9</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3856,8 +3854,8 @@
       <c r="F41" s="8" t="n">
         <v>25.4</v>
       </c>
-      <c r="G41" s="3" t="n">
-        <v>82.8</v>
+      <c r="G41" s="8" t="n">
+        <v>12.8</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>17</v>
@@ -3874,7 +3872,7 @@
       <c r="L41" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="M41" s="3" t="n">
+      <c r="M41" s="8" t="n">
         <v>20</v>
       </c>
       <c r="N41" s="3" t="inlineStr"/>
@@ -3884,7 +3882,7 @@
       <c r="P41" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q41" s="3" t="n">
+      <c r="Q41" s="8" t="n">
         <v>24.1</v>
       </c>
       <c r="R41" s="3" t="n">
@@ -3894,7 +3892,7 @@
         <v>27</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>59.2</v>
+        <v>59.8</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>9</v>
@@ -3906,7 +3904,7 @@
         <v>24.2</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>82.2</v>
+        <v>82.8</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>2.6</v>
@@ -3939,7 +3937,7 @@
         <v>25.6</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>2</v>
@@ -3953,11 +3951,11 @@
       <c r="L42" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="M42" s="3" t="n">
+      <c r="M42" s="8" t="n">
         <v>19.3</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="O42" s="3" t="n">
         <v>92.2</v>
@@ -3965,7 +3963,7 @@
       <c r="P42" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q42" s="3" t="n">
+      <c r="Q42" s="8" t="n">
         <v>25</v>
       </c>
       <c r="R42" s="3" t="n">
@@ -3975,13 +3973,13 @@
         <v>24.6</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>14.2</v>
+        <v>14.8</v>
       </c>
       <c r="U42" s="3" t="n">
         <v>3.6</v>
       </c>
       <c r="V42" s="13" t="n">
-        <v>0.1</v>
+        <v>2.8</v>
       </c>
       <c r="W42" s="13" t="n">
         <v>0.2</v>
@@ -4003,7 +4001,7 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D43" s="12" t="inlineStr"/>
       <c r="E43" s="12" t="inlineStr"/>
@@ -4014,11 +4012,11 @@
       <c r="J43" s="3" t="inlineStr"/>
       <c r="K43" s="8" t="inlineStr"/>
       <c r="L43" s="12" t="inlineStr"/>
-      <c r="M43" s="12" t="inlineStr"/>
+      <c r="M43" s="8" t="inlineStr"/>
       <c r="N43" s="3" t="inlineStr"/>
       <c r="O43" s="3" t="inlineStr"/>
       <c r="P43" s="3" t="inlineStr"/>
-      <c r="Q43" s="12" t="inlineStr"/>
+      <c r="Q43" s="8" t="inlineStr"/>
       <c r="R43" s="12" t="inlineStr"/>
       <c r="S43" s="3" t="inlineStr"/>
       <c r="T43" s="3" t="inlineStr"/>
@@ -4042,7 +4040,7 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D44" s="12" t="inlineStr"/>
       <c r="E44" s="12" t="inlineStr"/>
@@ -4053,11 +4051,11 @@
       <c r="J44" s="3" t="inlineStr"/>
       <c r="K44" s="8" t="inlineStr"/>
       <c r="L44" s="12" t="inlineStr"/>
-      <c r="M44" s="12" t="inlineStr"/>
+      <c r="M44" s="8" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="12" t="inlineStr"/>
+      <c r="Q44" s="8" t="inlineStr"/>
       <c r="R44" s="12" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
@@ -4081,16 +4079,16 @@
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr"/>
-      <c r="D45" s="14" t="n">
-        <v>122.3</v>
-      </c>
-      <c r="E45" s="14" t="n">
-        <v>34.6</v>
-      </c>
-      <c r="F45" s="14" t="n">
+      <c r="D45" s="8" t="n">
+        <v>129.4</v>
+      </c>
+      <c r="E45" s="8" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="F45" s="8" t="n">
         <v>102</v>
       </c>
-      <c r="G45" s="3" t="n">
+      <c r="G45" s="8" t="n">
         <v>54.7</v>
       </c>
       <c r="H45" s="3" t="n">
@@ -4106,32 +4104,32 @@
         <v>7.7</v>
       </c>
       <c r="L45" s="14" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="M45" s="14" t="n">
-        <v>11.1</v>
+        <v>97.59999999999999</v>
+      </c>
+      <c r="M45" s="8" t="n">
+        <v>77.09999999999999</v>
       </c>
       <c r="N45" s="3" t="inlineStr"/>
       <c r="O45" s="3" t="n">
-        <v>26.6</v>
+        <v>266.8</v>
       </c>
       <c r="P45" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q45" s="14" t="n">
-        <v>106.9</v>
+      <c r="Q45" s="8" t="n">
+        <v>106.7</v>
       </c>
       <c r="R45" s="14" t="n">
         <v>102.7</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>241.2</v>
+        <v>24.1</v>
       </c>
       <c r="T45" s="3" t="n">
         <v>38.7</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>96.3</v>
+        <v>95.3</v>
       </c>
       <c r="V45" s="14" t="n">
         <v>85.7</v>
@@ -4140,13 +4138,13 @@
         <v>96.3</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>327.2</v>
+        <v>32.7</v>
       </c>
       <c r="Y45" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>82.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4178,7 +4176,7 @@
         <v>17.5</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>13.7</v>
@@ -4189,20 +4187,20 @@
       <c r="L46" s="14" t="n">
         <v>12.4</v>
       </c>
-      <c r="M46" s="14" t="n">
-        <v>19.9</v>
+      <c r="M46" s="8" t="n">
+        <v>19.3</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>22.3</v>
+        <v>2.3</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>92.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="P46" s="3" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="Q46" s="8" t="n">
         <v>26.7</v>
-      </c>
-      <c r="Q46" s="14" t="n">
-        <v>0.2</v>
       </c>
       <c r="R46" s="14" t="n">
         <v>25.7</v>
@@ -4211,7 +4209,7 @@
         <v>22.9</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="U46" s="3" t="n">
         <v>29.8</v>
@@ -4225,9 +4223,7 @@
       <c r="X46" s="3" t="n">
         <v>60.2</v>
       </c>
-      <c r="Y46" s="3" t="n">
-        <v>2.1</v>
-      </c>
+      <c r="Y46" s="3" t="inlineStr"/>
       <c r="Z46" s="3" t="n">
         <v>298.9</v>
       </c>

--- a/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_recalcmultiday.xlsx
+++ b/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_recalcmultiday.xlsx
@@ -824,13 +824,13 @@
         <v>23.8</v>
       </c>
       <c r="S4" s="8" t="n">
-        <v>29.5</v>
+        <v>24.8</v>
       </c>
       <c r="T4" s="8" t="n">
-        <v>67.09999999999999</v>
+        <v>56.4</v>
       </c>
       <c r="U4" s="8" t="n">
-        <v>14.5</v>
+        <v>19.1</v>
       </c>
       <c r="V4" s="8" t="n">
         <v>27.5</v>
@@ -839,13 +839,13 @@
         <v>24.9</v>
       </c>
       <c r="X4" s="8" t="n">
-        <v>31.5</v>
+        <v>29.7</v>
       </c>
       <c r="Y4" s="8" t="n">
-        <v>85.7</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="Z4" s="8" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -907,13 +907,13 @@
         <v>21</v>
       </c>
       <c r="S5" s="8" t="n">
-        <v>24.9</v>
+        <v>22.9</v>
       </c>
       <c r="T5" s="8" t="n">
-        <v>83.8</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="U5" s="8" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="V5" s="8" t="n">
         <v>23.1</v>
@@ -922,13 +922,13 @@
         <v>21.3</v>
       </c>
       <c r="X5" s="8" t="n">
-        <v>25.3</v>
+        <v>24.1</v>
       </c>
       <c r="Y5" s="8" t="n">
-        <v>89.59999999999999</v>
+        <v>85.2</v>
       </c>
       <c r="Z5" s="8" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -990,13 +990,13 @@
         <v>24.1</v>
       </c>
       <c r="S6" s="8" t="n">
-        <v>30</v>
+        <v>26.3</v>
       </c>
       <c r="T6" s="8" t="n">
-        <v>72.8</v>
+        <v>63.8</v>
       </c>
       <c r="U6" s="8" t="n">
-        <v>11.2</v>
+        <v>14.9</v>
       </c>
       <c r="V6" s="8" t="n">
         <v>27.2</v>
@@ -1005,13 +1005,13 @@
         <v>22.6</v>
       </c>
       <c r="X6" s="8" t="n">
-        <v>27.4</v>
+        <v>24.3</v>
       </c>
       <c r="Y6" s="8" t="n">
-        <v>76</v>
+        <v>67.2</v>
       </c>
       <c r="Z6" s="8" t="n">
-        <v>8.699999999999999</v>
+        <v>11.8</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1058,13 +1058,13 @@
         <v>20.2</v>
       </c>
       <c r="N7" s="8" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="O7" s="8" t="n">
-        <v>99.40000000000001</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="P7" s="8" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q7" s="8" t="n">
         <v>20.1</v>
@@ -1073,13 +1073,13 @@
         <v>19.5</v>
       </c>
       <c r="S7" s="8" t="n">
-        <v>22.7</v>
+        <v>22.2</v>
       </c>
       <c r="T7" s="8" t="n">
-        <v>96.3</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="U7" s="8" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="V7" s="8" t="n">
         <v>21.4</v>
@@ -1088,13 +1088,13 @@
         <v>20.6</v>
       </c>
       <c r="X7" s="8" t="n">
-        <v>24.3</v>
+        <v>23.7</v>
       </c>
       <c r="Y7" s="8" t="n">
-        <v>95.2</v>
+        <v>93</v>
       </c>
       <c r="Z7" s="8" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1156,13 +1156,13 @@
         <v>22.3</v>
       </c>
       <c r="S8" s="8" t="n">
-        <v>26.9</v>
+        <v>24.5</v>
       </c>
       <c r="T8" s="8" t="n">
-        <v>81</v>
+        <v>73.8</v>
       </c>
       <c r="U8" s="8" t="n">
-        <v>6.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="V8" s="8" t="n">
         <v>24.6</v>
@@ -1171,13 +1171,13 @@
         <v>21.4</v>
       </c>
       <c r="X8" s="8" t="n">
-        <v>25.5</v>
+        <v>23.3</v>
       </c>
       <c r="Y8" s="8" t="n">
-        <v>82.40000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="Z8" s="8" t="n">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1322,13 +1322,13 @@
         <v>22</v>
       </c>
       <c r="S10" s="8" t="n">
-        <v>26.4</v>
+        <v>23.8</v>
       </c>
       <c r="T10" s="8" t="n">
-        <v>79.09999999999999</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="U10" s="8" t="n">
-        <v>7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="V10" s="8" t="n">
         <v>24.8</v>
@@ -1337,13 +1337,13 @@
         <v>22.2</v>
       </c>
       <c r="X10" s="8" t="n">
-        <v>26.8</v>
+        <v>25</v>
       </c>
       <c r="Y10" s="8" t="n">
-        <v>85.5</v>
+        <v>79.8</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>4.5</v>
+        <v>6.3</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
       <c r="W12" s="8" t="n">
         <v>21.1</v>
       </c>
-      <c r="X12" s="3" t="n">
+      <c r="X12" s="8" t="n">
         <v>24.4</v>
       </c>
       <c r="Y12" s="3" t="n">
@@ -1573,19 +1573,19 @@
       <c r="U13" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="V13" s="3" t="n">
+      <c r="V13" s="8" t="n">
         <v>21.2</v>
       </c>
       <c r="W13" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="X13" s="3" t="n">
+      <c r="X13" s="8" t="n">
         <v>22.6</v>
       </c>
-      <c r="Y13" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z13" s="3" t="n">
+      <c r="Y13" s="8" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="Z13" s="8" t="n">
         <v>2.5</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
@@ -1747,7 +1747,7 @@
       <c r="W15" s="8" t="n">
         <v>20.9</v>
       </c>
-      <c r="X15" s="3" t="n">
+      <c r="X15" s="8" t="n">
         <v>24.4</v>
       </c>
       <c r="Y15" s="3" t="n">
